--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -832,6 +832,15 @@
   </si>
   <si>
     <t xml:space="preserve">Y or N (see description)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI INSIGHTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enable_ai_insights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate AI-powered callout insights alongside crosstab tables in the HTML report. Requires an Anthropic API key set in the ANTHROPIC_API_KEY environment variable. Leave FALSE if you do not have an API key or do not need AI commentary.</t>
   </si>
   <si>
     <t xml:space="preserve">STUDY IDENTIFICATION</t>
@@ -3375,7 +3384,7 @@
         <v>273</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C113" s="16" t="s">
         <v>4</v>
@@ -3384,29 +3393,21 @@
         <v>274</v>
       </c>
       <c r="E113" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C114" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E114" s="14" t="s">
-        <v>275</v>
-      </c>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>36</v>
@@ -3415,14 +3416,48 @@
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E115" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="E115" s="14" t="s">
-        <v>275</v>
+      <c r="B116" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="E116" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E117" s="14" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
@@ -3441,6 +3476,7 @@
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A114:E114"/>
   </mergeCells>
   <dataValidations count="20">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B17:B17">
@@ -3528,7 +3564,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="37">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="38">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx,csv"</xm:f>
@@ -3751,6 +3787,12 @@
           </x14:formula1>
           <xm:sqref>B111:B111</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"FALSE,TRUE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B113:B113</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -3776,99 +3818,99 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>36</v>
@@ -3877,30 +3919,30 @@
         <v>36</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>36</v>
@@ -3909,18 +3951,18 @@
         <v>36</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>128</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>36</v>
@@ -3941,7 +3983,7 @@
         <v>36</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8">
@@ -4602,122 +4644,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -4742,42 +4784,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -4785,10 +4827,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>36</v>
@@ -4796,10 +4838,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>36</v>
@@ -4977,42 +5019,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -5020,10 +5062,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="393">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -597,12 +597,21 @@
     <t xml:space="preserve">#CC9900</t>
   </si>
   <si>
-    <t xml:space="preserve">Accent colour for HTML report highlights and call-outs.</t>
+    <t xml:space="preserve">Accent colour for HTML report highlights and call-outs. Also used as the default crosstab heatmap tint colour.</t>
   </si>
   <si>
     <t xml:space="preserve">Hex colour code (e.g. #CC9900)</t>
   </si>
   <si>
+    <t xml:space="preserve">heatmap_colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crosstab heatmap cell tint colour. Defaults to accent_colour (warm cream for standard #CC9900). Set explicitly to override without affecting other colours (e.g. #323367 for cool blue).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code, or leave blank to use accent_colour</t>
+  </si>
+  <si>
     <t xml:space="preserve">chart_bar_colour</t>
   </si>
   <si>
@@ -745,6 +754,69 @@
   </si>
   <si>
     <t xml:space="preserve">File path (deprecated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA-CENTRIC REPORT V2 (OPTIONAL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_report_v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also build the interactive, self-contained data-centric report v2 (live audience filter, custom banners, confidence intervals). Additive: the classic Excel/HTML outputs are unchanged. See docs/11_DATA_CENTRIC_REPORT_V2.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sampling_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not_Specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample design — drives honest confidence vocabulary in the v2 report (probability designs speak confidence intervals / margin of error; otherwise stability intervals / point estimates).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not_Specified, Random, Stratified, Cluster, Census, Convenience, Quota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave label shown in the v2 report header and used as the tracking trend label (e.g. Wave 25 - May 2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free text, or leave blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_report_v2_tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a Tracking tab to the v2 report, built from anonymised per-wave microdata. Requires html_report_v2=TRUE and a waves_source with prior waves' contributions. The standalone tracker module is unaffected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">waves_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folder holding prior waves' *_wave.json tracking contributions (each wave's own tabs run writes one). Blank -&gt; no history, Tracking tab stays hidden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folder path, or leave blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wave_order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric x-axis order key for this wave (e.g. 2025.5 so two same-year waves never collide). Blank -&gt; a 4-digit year is parsed from the wave label.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (e.g. 2026 or 2025.5), or leave blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">question_mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to the classic tracker's Question_Mapping.xlsx. Links waves by a canonical key (robust to question renames) + curates which metrics track. Blank -&gt; auto-detected in waves_source, else metrics match by question title.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File path, or leave blank to auto-detect</t>
   </si>
   <si>
     <t xml:space="preserve">ROW DESCRIPTORS (HTML Report)</t>
@@ -2894,28 +2966,28 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="15" t="s">
         <v>195</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>196</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>15</v>
@@ -2924,18 +2996,18 @@
         <v>199</v>
       </c>
       <c r="E84" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="15" t="s">
+      <c r="B85" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B85" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C85" s="16" t="s">
-        <v>4</v>
+      <c r="C85" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>202</v>
@@ -3064,76 +3136,76 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="15" t="s">
         <v>225</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E93" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="B94" s="11" t="s">
+    <row r="95">
+      <c r="A95" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B95" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C94" s="16" t="s">
+      <c r="C95" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B95" s="11" t="s">
+      <c r="D95" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C95" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" s="13" t="s">
+      <c r="E95" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="E95" s="14" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="96">
-      <c r="A96" s="15" t="s">
+      <c r="A96" s="10" t="s">
         <v>233</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C96" s="16" t="s">
-        <v>4</v>
+        <v>234</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>36</v>
@@ -3142,10 +3214,10 @@
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98">
@@ -3162,12 +3234,12 @@
         <v>239</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>36</v>
@@ -3176,44 +3248,44 @@
         <v>4</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
+      <c r="B100" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C101" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="E101" s="14" t="s">
+      <c r="A101" s="9" t="s">
         <v>246</v>
       </c>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
     </row>
     <row r="102">
       <c r="A102" s="15" t="s">
         <v>247</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C102" s="16" t="s">
         <v>4</v>
@@ -3222,15 +3294,15 @@
         <v>248</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>249</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B103" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="C103" s="16" t="s">
         <v>4</v>
@@ -3256,21 +3328,29 @@
         <v>254</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
+      <c r="A105" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>36</v>
@@ -3279,15 +3359,15 @@
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>36</v>
@@ -3296,15 +3376,15 @@
         <v>4</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>36</v>
@@ -3313,32 +3393,24 @@
         <v>4</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="B109" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C109" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>237</v>
-      </c>
+      <c r="A109" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
     </row>
     <row r="110">
       <c r="A110" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>36</v>
@@ -3347,58 +3419,66 @@
         <v>4</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="C111" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="B112" s="9"/>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
+      <c r="A112" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E112" s="14" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C113" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>34</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -3407,7 +3487,7 @@
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>36</v>
@@ -3416,15 +3496,15 @@
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>36</v>
@@ -3433,15 +3513,15 @@
         <v>4</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="15" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B117" s="11" t="s">
         <v>36</v>
@@ -3450,14 +3530,151 @@
         <v>4</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>278</v>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="E118" s="14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E119" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E120" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="E122" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="E125" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="E126" s="14" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
@@ -3473,10 +3690,11 @@
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A123:E123"/>
   </mergeCells>
   <dataValidations count="20">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B17:B17">
@@ -3564,7 +3782,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="38">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="41">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx,csv"</xm:f>
@@ -3773,25 +3991,43 @@
           <x14:formula1>
             <xm:f>"warm,cool,research,teal,red,brand"</xm:f>
           </x14:formula1>
-          <xm:sqref>B84:B84</xm:sqref>
+          <xm:sqref>B85:B85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B93:B93</xm:sqref>
+          <xm:sqref>B94:B94</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B102:B102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Convenience,Quota"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B103:B103</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B105:B105</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B111:B111</xm:sqref>
+          <xm:sqref>B120:B120</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B113:B113</xm:sqref>
+          <xm:sqref>B122:B122</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3818,99 +4054,99 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>36</v>
@@ -3919,30 +4155,30 @@
         <v>36</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>36</v>
@@ -3951,18 +4187,18 @@
         <v>36</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>128</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>36</v>
@@ -3983,7 +4219,7 @@
         <v>36</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -4644,122 +4880,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -4784,42 +5020,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -4827,10 +5063,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>36</v>
@@ -4838,10 +5074,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>36</v>
@@ -5019,42 +5255,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -5062,10 +5298,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -11,12 +11,13 @@
     <sheet name="Base Filters Reference" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Comments" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="AddedSlides" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Population" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -774,7 +775,16 @@
     <t xml:space="preserve">Sample design — drives honest confidence vocabulary in the v2 report (probability designs speak confidence intervals / margin of error; otherwise stability intervals / point estimates).</t>
   </si>
   <si>
-    <t xml:space="preserve">Not_Specified, Random, Stratified, Cluster, Census, Convenience, Quota</t>
+    <t xml:space="preserve">Not_Specified, Random, Stratified, Cluster, Census, Quota, Online_Panel, Convenience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">population_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total universe size for a census / full-invite study (e.g. all staff or students invited). Enables the finite population correction in the v2 report: intervals narrow as coverage of the universe rises, and a small base that is most of a known group is no longer flagged unstable. Per-group sizes go in the optional Population sheet. Blank = no correction (intervals behave as an infinite-population sample).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole number greater than 1, or leave blank</t>
   </si>
   <si>
     <t xml:space="preserve">wave</t>
@@ -913,6 +923,18 @@
   </si>
   <si>
     <t xml:space="preserve">Generate AI-powered callout insights alongside crosstab tables in the HTML report. Requires an Anthropic API key set in the ANTHROPIC_API_KEY environment variable. Leave FALSE if you do not have an API key or do not need AI commentary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ai_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonnet 4.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which AI model writes the insights (only used when enable_ai_insights = TRUE). Choose 'Sonnet 4.6' (faster, lower cost) or 'Opus 4.8' (highest quality). Advanced: type any exact model ID (e.g. claude-sonnet-4-6) to use a newer model without waiting for a template update. Leave blank to drive the model from the AI sidecar file instead (needed when switching to a non-Anthropic provider).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonnet 4.6, Opus 4.8, or an exact model ID</t>
   </si>
   <si>
     <t xml:space="preserve">STUDY IDENTIFICATION</t>
@@ -1197,6 +1219,36 @@
     <t xml:space="preserve">- Focus on improving customer service touchpoints
 - Invest in digital channel experience
 - Monitor competitor NPS quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known Group Sizes (Finite Population Correction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIONAL. For a census / full-invite study, give each banner column's universe size so its intervals and significance reflect how much of the group responded. The study total goes in the population_size setting. Leave the whole sheet blank for no correction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Banner column / subgroup label EXACTLY as it appears in the report (e.g. Masters, Honours, Cape Town).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Total number of people in that group's universe (e.g. the cohort enrolment). Whole number greater than 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Optional: the banner question this group belongs to (e.g. Year). Leave blank to match the Group label across any banner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honours</t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3388,7 @@
         <v>256</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C105" s="16" t="s">
         <v>4</v>
@@ -3345,24 +3397,24 @@
         <v>257</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>34</v>
+        <v>258</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C106" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>260</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107">
@@ -3400,30 +3452,30 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="s">
+      <c r="A109" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="B109" s="9"/>
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
+      <c r="B109" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E109" s="14" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C110" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="E110" s="14" t="s">
+      <c r="A110" s="9" t="s">
         <v>270</v>
       </c>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
     </row>
     <row r="111">
       <c r="A111" s="15" t="s">
@@ -3473,38 +3525,38 @@
         <v>278</v>
       </c>
       <c r="E113" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E114" s="14" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
-    </row>
     <row r="115">
-      <c r="A115" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C115" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="E115" s="14" t="s">
-        <v>232</v>
-      </c>
+      <c r="A115" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
     </row>
     <row r="116">
       <c r="A116" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>36</v>
@@ -3513,10 +3565,10 @@
         <v>4</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117">
@@ -3550,12 +3602,12 @@
         <v>289</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>36</v>
@@ -3564,10 +3616,10 @@
         <v>4</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>292</v>
+        <v>240</v>
       </c>
     </row>
     <row r="120">
@@ -3575,7 +3627,7 @@
         <v>293</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="C120" s="16" t="s">
         <v>4</v>
@@ -3588,77 +3640,77 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="s">
+      <c r="A121" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
+      <c r="B121" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="E121" s="14" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="B122" s="11" t="s">
+      <c r="A122" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B123" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C122" s="16" t="s">
+      <c r="C123" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="E122" s="14" t="s">
+      <c r="D123" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E123" s="14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>36</v>
+        <v>303</v>
       </c>
       <c r="C124" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="B125" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C125" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>302</v>
-      </c>
+      <c r="A125" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
     </row>
     <row r="126">
       <c r="A126" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>36</v>
@@ -3667,10 +3719,44 @@
         <v>4</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>302</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="E127" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E128" s="14" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3691,10 +3777,10 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A79:E79"/>
     <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
   </mergeCells>
   <dataValidations count="20">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B17:B17">
@@ -3782,7 +3868,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="41">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="42">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx,csv"</xm:f>
@@ -4007,7 +4093,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Convenience,Quota"</xm:f>
+            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
           </x14:formula1>
           <xm:sqref>B103:B103</xm:sqref>
         </x14:dataValidation>
@@ -4015,19 +4101,25 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B105:B105</xm:sqref>
+          <xm:sqref>B106:B106</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B120:B120</xm:sqref>
+          <xm:sqref>B121:B121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B122:B122</xm:sqref>
+          <xm:sqref>B123:B123</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B124:B124</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4054,99 +4146,99 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>36</v>
@@ -4155,30 +4247,30 @@
         <v>36</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>36</v>
@@ -4187,18 +4279,18 @@
         <v>36</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>128</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>36</v>
@@ -4219,7 +4311,7 @@
         <v>36</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8">
@@ -4880,122 +4972,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -5020,42 +5112,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -5063,10 +5155,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>36</v>
@@ -5074,10 +5166,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>36</v>
@@ -5255,42 +5347,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -5298,10 +5390,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -5421,4 +5513,234 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="34.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B5:B36">
+      <formula1>2</formula1>
+      <formula2>10000000</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Dev/Turas/modules/tabs/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A3881B-6F2F-F14E-BD24-7DD1E13E3671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAAA661-30B4-8248-AD87-317274ED18C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="19480" windowHeight="11520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="418">
   <si>
     <t>TURAS Crosstab Configuration</t>
   </si>
@@ -1269,6 +1269,18 @@
   </si>
   <si>
     <t>set the order of the category</t>
+  </si>
+  <si>
+    <t>CommentSheet</t>
+  </si>
+  <si>
+    <t>CommentLink</t>
+  </si>
+  <si>
+    <t>The sheet containing open ended comments</t>
+  </si>
+  <si>
+    <t>The close ended question the comments link to</t>
   </si>
 </sst>
 </file>
@@ -3812,26 +3824,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A79:E79"/>
     <mergeCell ref="A101:E101"/>
     <mergeCell ref="A110:E110"/>
     <mergeCell ref="A115:E115"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <dataValidations count="21">
     <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" sqref="B77:B78 B71:B72 B17:B18" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3913,7 +3925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -3924,11 +3936,11 @@
     <col min="6" max="6" width="14.6640625" customWidth="1"/>
     <col min="7" max="7" width="13.6640625" customWidth="1"/>
     <col min="8" max="8" width="35.6640625" customWidth="1"/>
-    <col min="9" max="11" width="30.6640625" customWidth="1"/>
-    <col min="12" max="12" width="40.6640625" customWidth="1"/>
+    <col min="9" max="13" width="30.6640625" customWidth="1"/>
+    <col min="14" max="14" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>314</v>
       </c>
@@ -3943,8 +3955,10 @@
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
       <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>315</v>
       </c>
@@ -3959,8 +3973,10 @@
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
       <c r="L2" s="16"/>
-    </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+    </row>
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>316</v>
       </c>
@@ -3995,10 +4011,16 @@
         <v>411</v>
       </c>
       <c r="L3" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>326</v>
       </c>
@@ -4033,10 +4055,16 @@
         <v>413</v>
       </c>
       <c r="L4" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="N4" s="10" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>336</v>
       </c>
@@ -4066,11 +4094,13 @@
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>339</v>
       </c>
@@ -4100,11 +4130,13 @@
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>342</v>
       </c>
@@ -4134,11 +4166,13 @@
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -4151,8 +4185,10 @@
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -4165,8 +4201,10 @@
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -4179,8 +4217,10 @@
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -4193,8 +4233,10 @@
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -4207,8 +4249,10 @@
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -4221,8 +4265,10 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -4235,8 +4281,10 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4249,8 +4297,10 @@
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -4263,8 +4313,10 @@
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -4277,8 +4329,10 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -4291,8 +4345,10 @@
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -4305,8 +4361,10 @@
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -4319,8 +4377,10 @@
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -4333,8 +4393,10 @@
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -4347,8 +4409,10 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -4361,8 +4425,10 @@
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -4375,8 +4441,10 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -4389,8 +4457,10 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -4403,8 +4473,10 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -4417,8 +4489,10 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -4431,8 +4505,10 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4445,8 +4521,10 @@
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -4459,8 +4537,10 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -4473,8 +4553,10 @@
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -4487,8 +4569,10 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -4501,8 +4585,10 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -4515,8 +4601,10 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4529,8 +4617,10 @@
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -4543,8 +4633,10 @@
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -4557,8 +4649,10 @@
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -4571,8 +4665,10 @@
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -4585,8 +4681,10 @@
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -4599,8 +4697,10 @@
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -4613,8 +4713,10 @@
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -4627,8 +4729,10 @@
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -4641,8 +4745,10 @@
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -4655,8 +4761,10 @@
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -4669,8 +4777,10 @@
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -4683,8 +4793,10 @@
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -4697,8 +4809,10 @@
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -4711,8 +4825,10 @@
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -4725,8 +4841,10 @@
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -4739,8 +4857,10 @@
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -4753,8 +4873,10 @@
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -4767,8 +4889,10 @@
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -4781,8 +4905,10 @@
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -4795,8 +4921,10 @@
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -4809,8 +4937,10 @@
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -4823,8 +4953,10 @@
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -4837,11 +4969,13 @@
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F57" xr:uid="{00000000-0002-0000-0100-000000000000}">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -167,30 +167,6 @@
   </si>
   <si>
     <t xml:space="preserve">Any descriptive text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight_na_threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum % of missing weight values before a warning is issued.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 to 100 (percentage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight_zero_threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum % of zero weight values before a warning is issued.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight_deff_warning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design Effect threshold: warn if DEFF exceeds this value (high = low efficiency).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 to 10 (typical: 2-3)</t>
   </si>
   <si>
     <t xml:space="preserve">DISPLAY OPTIONS</t>
@@ -2217,68 +2193,68 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>52</v>
-      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>5</v>
+        <v>51</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>3</v>
+        <v>53</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>40</v>
@@ -2287,7 +2263,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>34</v>
@@ -2295,7 +2271,7 @@
     </row>
     <row r="23">
       <c r="A23" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>40</v>
@@ -2304,24 +2280,24 @@
         <v>15</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="s">
-        <v>63</v>
+      <c r="A24" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>15</v>
+      <c r="C24" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>34</v>
@@ -2329,87 +2305,87 @@
     </row>
     <row r="25">
       <c r="A25" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="12" t="s">
+      <c r="C27" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D27" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="s">
+      <c r="E27" s="14" t="s">
         <v>69</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>32</v>
+        <v>70</v>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="B29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="11" t="s">
         <v>75</v>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>15</v>
@@ -2418,106 +2394,98 @@
         <v>76</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B31" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>80</v>
-      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>1</v>
+        <v>80</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>1</v>
+        <v>82</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E34" s="14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>40</v>
@@ -2526,7 +2494,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>34</v>
@@ -2534,121 +2502,129 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>32</v>
+        <v>89</v>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>0.05</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="s">
+      <c r="E39" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>15</v>
+      <c r="B40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>96</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>0.05</v>
+        <v>98</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>15</v>
+      <c r="B42" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>101</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>1</v>
+        <v>102</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="B44" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="s">
+      <c r="E44" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>4</v>
@@ -2657,72 +2633,72 @@
         <v>109</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B46" s="11" t="s">
+      <c r="A46" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>4</v>
+      <c r="C47" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>113</v>
       </c>
       <c r="E47" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="s">
+      <c r="B48" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="E48" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="13" t="s">
+      <c r="B49" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E48" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
+      <c r="E49" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>32</v>
@@ -2731,7 +2707,7 @@
         <v>15</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>34</v>
@@ -2739,53 +2715,45 @@
     </row>
     <row r="51">
       <c r="A51" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="54">
@@ -2793,213 +2761,213 @@
         <v>128</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E54" s="14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="s">
+      <c r="B55" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
+      <c r="E55" s="14" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="s">
         <v>132</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E57" s="14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="s">
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C58" s="12" t="s">
+      <c r="B59" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="12" t="s">
+      <c r="D61" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B60" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="12" t="s">
+      <c r="D63" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E60" s="14" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="s">
+      <c r="D65" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
+      <c r="E65" s="14" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>156</v>
-      </c>
+      <c r="A67" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B68" s="11" t="s">
         <v>158</v>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>15</v>
@@ -3015,34 +2983,42 @@
       <c r="A69" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B69" s="11" t="s">
-        <v>162</v>
+      <c r="B69" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="B70" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="13" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="s">
+      <c r="E70" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="s">
         <v>166</v>
       </c>
       <c r="B71" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>15</v>
@@ -3051,24 +3027,24 @@
         <v>167</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B72" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E72" s="14" t="s">
         <v>170</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="73">
@@ -3076,7 +3052,7 @@
         <v>171</v>
       </c>
       <c r="B73" s="11" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>15</v>
@@ -3085,191 +3061,191 @@
         <v>172</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B74" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B75" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B76" s="11" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B77" s="11" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B78" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>178</v>
-      </c>
+      <c r="A78" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B79" s="11" t="n">
-        <v>60</v>
+        <v>182</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B80" s="11" t="n">
-        <v>40</v>
+        <v>184</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>185</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E80" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="s">
+      <c r="B81" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
+      <c r="C81" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="s">
-        <v>190</v>
+      <c r="A82" s="15" t="s">
+        <v>192</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>34</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>36</v>
@@ -3278,49 +3254,49 @@
         <v>4</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="s">
-        <v>203</v>
+      <c r="A86" s="15" t="s">
+        <v>204</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="s">
-        <v>205</v>
+      <c r="A87" s="15" t="s">
+        <v>207</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>36</v>
@@ -3329,15 +3305,15 @@
         <v>4</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>36</v>
@@ -3346,15 +3322,15 @@
         <v>4</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>36</v>
@@ -3363,15 +3339,15 @@
         <v>4</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>36</v>
@@ -3380,15 +3356,15 @@
         <v>4</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>36</v>
@@ -3397,27 +3373,27 @@
         <v>4</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="s">
-        <v>224</v>
+      <c r="A93" s="10" t="s">
+        <v>225</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C93" s="16" t="s">
-        <v>4</v>
+        <v>40</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>226</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94">
@@ -3438,37 +3414,37 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="15" t="s">
+      <c r="A95" s="10" t="s">
         <v>230</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C95" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96" s="16" t="s">
         <v>4</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="E95" s="14" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>15</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>234</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>34</v>
+        <v>229</v>
       </c>
     </row>
     <row r="97">
@@ -3489,17 +3465,17 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="15" t="s">
         <v>238</v>
       </c>
       <c r="B98" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="13" t="s">
         <v>239</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>240</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>237</v>
@@ -3507,7 +3483,7 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>36</v>
@@ -3516,78 +3492,78 @@
         <v>4</v>
       </c>
       <c r="D99" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E99" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="E99" s="14" t="s">
-        <v>237</v>
-      </c>
     </row>
     <row r="100">
-      <c r="A100" s="15" t="s">
+      <c r="A100" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B100" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C100" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>245</v>
-      </c>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
     </row>
     <row r="101">
       <c r="A101" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C101" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>245</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C102" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D102" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D103" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="E102" s="14" t="s">
+      <c r="E103" s="14" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
     </row>
     <row r="104">
       <c r="A104" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B104" s="11" t="s">
         <v>252</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="C104" s="16" t="s">
         <v>4</v>
@@ -3596,29 +3572,29 @@
         <v>253</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>34</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C105" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>34</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>36</v>
@@ -3627,18 +3603,18 @@
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>260</v>
+        <v>32</v>
       </c>
       <c r="C107" s="16" t="s">
         <v>4</v>
@@ -3647,12 +3623,12 @@
         <v>261</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>36</v>
@@ -3661,15 +3637,15 @@
         <v>4</v>
       </c>
       <c r="D108" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E108" s="14" t="s">
         <v>264</v>
-      </c>
-      <c r="E108" s="14" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>36</v>
@@ -3678,10 +3654,10 @@
         <v>4</v>
       </c>
       <c r="D109" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="E109" s="14" t="s">
         <v>267</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="110">
@@ -3689,7 +3665,7 @@
         <v>268</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C110" s="16" t="s">
         <v>4</v>
@@ -3698,29 +3674,21 @@
         <v>269</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C111" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D111" s="13" t="s">
+      <c r="A111" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="E111" s="14" t="s">
-        <v>272</v>
-      </c>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
     </row>
     <row r="112">
       <c r="A112" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>36</v>
@@ -3729,15 +3697,15 @@
         <v>4</v>
       </c>
       <c r="D112" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E112" s="14" t="s">
         <v>274</v>
-      </c>
-      <c r="E112" s="14" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>36</v>
@@ -3746,15 +3714,15 @@
         <v>4</v>
       </c>
       <c r="D113" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E113" s="14" t="s">
         <v>277</v>
-      </c>
-      <c r="E113" s="14" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -3763,41 +3731,41 @@
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C115" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C116" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>285</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -3806,50 +3774,58 @@
     </row>
     <row r="118">
       <c r="A118" s="15" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C118" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>34</v>
+        <v>286</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C119" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D119" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="E119" s="14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="E119" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="s">
+      <c r="B120" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="B120" s="9"/>
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
+      <c r="E120" s="14" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>36</v>
@@ -3858,32 +3834,24 @@
         <v>4</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>294</v>
+        <v>229</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="s">
+      <c r="A122" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="B122" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C122" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D122" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="E122" s="14" t="s">
-        <v>297</v>
-      </c>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
     </row>
     <row r="123">
       <c r="A123" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>36</v>
@@ -3892,15 +3860,15 @@
         <v>4</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>36</v>
@@ -3909,20 +3877,28 @@
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D125" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="E124" s="14" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="s">
+      <c r="E125" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
     </row>
     <row r="126">
       <c r="A126" s="15" t="s">
@@ -3963,7 +3939,7 @@
         <v>309</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="C128" s="16" t="s">
         <v>4</v>
@@ -3976,59 +3952,51 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="s">
+      <c r="A129" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="B129" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C129" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="E129" s="14" t="s">
-        <v>245</v>
-      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
     </row>
     <row r="130">
       <c r="A130" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C130" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>316</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>133</v>
+        <v>316</v>
       </c>
       <c r="C131" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D131" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="E131" s="14" t="s">
         <v>318</v>
-      </c>
-      <c r="E131" s="14" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
@@ -4037,19 +4005,19 @@
     </row>
     <row r="133">
       <c r="A133" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C133" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D133" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E133" s="14" t="s">
         <v>322</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="134">
@@ -4057,21 +4025,21 @@
         <v>323</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>324</v>
+        <v>36</v>
       </c>
       <c r="C134" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -4080,7 +4048,7 @@
     </row>
     <row r="136">
       <c r="A136" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>36</v>
@@ -4089,58 +4057,66 @@
         <v>4</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E136" s="14" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>36</v>
+        <v>330</v>
       </c>
       <c r="C137" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D137" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E137" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="E137" s="14" t="s">
-        <v>330</v>
-      </c>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="s">
+      <c r="A138" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="B138" s="9"/>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
+      <c r="B138" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="E138" s="14" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>36</v>
+        <v>338</v>
       </c>
       <c r="C139" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="15" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>338</v>
@@ -4149,95 +4125,44 @@
         <v>4</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="15" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>342</v>
+        <v>36</v>
       </c>
       <c r="C141" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>346</v>
+        <v>36</v>
       </c>
       <c r="C142" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="15" t="s">
         <v>349</v>
-      </c>
-      <c r="B143" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="C143" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="E143" s="14" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="B144" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C144" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="E144" s="14" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="B145" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C145" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="E145" s="14" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -4246,84 +4171,84 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A111:E111"/>
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A120:E120"/>
-    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A129:E129"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A135:E135"/>
-    <mergeCell ref="A138:E138"/>
   </mergeCells>
-  <dataValidations count="21">
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B18:B18">
+  <dataValidations count="18">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B28:B28">
       <formula1>0</formula1>
-      <formula2>100</formula2>
+      <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B19:B19">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B29:B29">
       <formula1>0</formula1>
-      <formula2>100</formula2>
+      <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B20:B20">
-      <formula1>1</formula1>
-      <formula2>10</formula2>
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B30:B30">
+      <formula1>0</formula1>
+      <formula2>4</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B31:B31">
       <formula1>0</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B32:B32">
-      <formula1>0</formula1>
-      <formula2>4</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B33:B33">
-      <formula1>0</formula1>
-      <formula2>4</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B34:B34">
-      <formula1>0</formula1>
-      <formula2>4</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B41:B41">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B38:B38">
       <formula1>0.001</formula1>
       <formula2>0.5</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B42:B42">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B39:B39">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43:B43">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B40:B40">
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B60:B60">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B57:B57">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B71:B71">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B68:B68">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B72:B72">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B69:B69">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B73:B73">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B70:B70">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B74:B74">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B71:B71">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B72:B72">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B73:B73">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B74:B74">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -4331,23 +4256,11 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B76:B76">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B76:B76">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B77:B77">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B78:B78">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B79:B79">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B80:B80">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B77:B77">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -4391,6 +4304,24 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
+          <xm:sqref>B19:B19</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B20:B20</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B21:B21</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
           <xm:sqref>B22:B22</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
@@ -4399,7 +4330,7 @@
           </x14:formula1>
           <xm:sqref>B23:B23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
@@ -4413,13 +4344,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B26:B26</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>".,,"</xm:f>
           </x14:formula1>
           <xm:sqref>B27:B27</xm:sqref>
         </x14:dataValidation>
@@ -4427,19 +4352,19 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B28:B28</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>".,,"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B30:B30</xm:sqref>
+          <xm:sqref>B33:B33</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B36:B36</xm:sqref>
+          <xm:sqref>B34:B34</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B35:B35</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4451,37 +4376,43 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B38:B38</xm:sqref>
+          <xm:sqref>B41:B41</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B42:B42</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B43:B43</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"primary,secondary"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B45:B45</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B40:B40</xm:sqref>
+          <xm:sqref>B47:B47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B44:B44</xm:sqref>
+          <xm:sqref>B48:B48</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B45:B45</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B46:B46</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"primary,secondary"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B48:B48</xm:sqref>
+          <xm:sqref>B49:B49</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4491,25 +4422,19 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"IQR"</xm:f>
           </x14:formula1>
           <xm:sqref>B51:B51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B52:B52</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"Y,N"</xm:f>
           </x14:formula1>
           <xm:sqref>B53:B53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"IQR"</xm:f>
+            <xm:f>"Y,N"</xm:f>
           </x14:formula1>
           <xm:sqref>B54:B54</xm:sqref>
         </x14:dataValidation>
@@ -4517,71 +4442,71 @@
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B56:B56</xm:sqref>
+          <xm:sqref>B55:B55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B57:B57</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B58:B58</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B59:B59</xm:sqref>
+          <xm:sqref>B56:B56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B62:B62</xm:sqref>
+          <xm:sqref>B59:B59</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B64:B64</xm:sqref>
+          <xm:sqref>B61:B61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B66:B66</xm:sqref>
+          <xm:sqref>B63:B63</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"desc,asc,alphabetic"</xm:f>
           </x14:formula1>
-          <xm:sqref>B69:B69</xm:sqref>
+          <xm:sqref>B66:B66</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B82:B82</xm:sqref>
+          <xm:sqref>B79:B79</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"warm,cool,research,teal,red,brand"</xm:f>
           </x14:formula1>
-          <xm:sqref>B87:B87</xm:sqref>
+          <xm:sqref>B84:B84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B96:B96</xm:sqref>
+          <xm:sqref>B93:B93</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B101:B101</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B102:B102</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
           </x14:formula1>
           <xm:sqref>B104:B104</xm:sqref>
         </x14:dataValidation>
@@ -4589,73 +4514,61 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B105:B105</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
-          </x14:formula1>
           <xm:sqref>B107:B107</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B110:B110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B118:B118</xm:sqref>
+          <xm:sqref>B115:B115</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B119:B119</xm:sqref>
+          <xm:sqref>B116:B116</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B131:B131</xm:sqref>
+          <xm:sqref>B128:B128</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B133:B133</xm:sqref>
+          <xm:sqref>B130:B130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
           </x14:formula1>
-          <xm:sqref>B134:B134</xm:sqref>
+          <xm:sqref>B131:B131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B140:B140</xm:sqref>
+          <xm:sqref>B137:B137</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B141:B141</xm:sqref>
+          <xm:sqref>B138:B138</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B142:B142</xm:sqref>
+          <xm:sqref>B139:B139</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B143:B143</xm:sqref>
+          <xm:sqref>B140:B140</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4691,153 +4604,153 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="S3" s="8" t="s">
         <v>370</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="J4" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="K4" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="L4" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="M4" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="N4" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="O4" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="P4" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="Q4" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="R4" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="S4" s="13" t="s">
         <v>389</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q4" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>36</v>
@@ -4873,30 +4786,30 @@
         <v>36</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>36</v>
@@ -4932,18 +4845,18 @@
         <v>36</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>36</v>
@@ -4955,7 +4868,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>36</v>
@@ -4991,57 +4904,57 @@
         <v>36</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B8" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>399</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>399</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>407</v>
-      </c>
       <c r="P8" s="17" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="Q8" s="17" t="s">
         <v>36</v>
@@ -5050,18 +4963,18 @@
         <v>36</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>36</v>
@@ -5073,7 +4986,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>36</v>
@@ -5097,19 +5010,19 @@
         <v>36</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10">
@@ -6230,122 +6143,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -6371,48 +6284,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -6423,10 +6336,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>36</v>
@@ -6437,16 +6350,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8">
@@ -6651,42 +6564,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6694,10 +6607,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6831,56 +6744,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -307,7 +307,7 @@
     <t xml:space="preserve">min_reporting_base</t>
   </si>
   <si>
-    <t xml:space="preserve">Disclosure control: minimum audience below which the report hides identifying detail (comment demographic tags; small cells) so a filter cannot narrow onto identifiable people. 1 = off. Use ~10 for a small/sensitive sample (e.g. a staff climate survey); set it to the full sample size to forbid any sub-group drill-down.</t>
+    <t xml:space="preserve">Disclosure control: minimum audience below which the report hides identifying detail (comment demographic tags; small cells) so a filter cannot narrow onto identifiable people. 1 = off. Use ~10 for a small/sensitive sample (e.g. a staff climate survey); set it to the full sample size to forbid any sub-group drill-down. NOTE: this gates the SCREEN; for a k-gate that must hold in the shipped FILE, also set html_report_v2_microdata = FALSE (the confidential ship).</t>
   </si>
   <si>
     <t xml:space="preserve">1 to 100000 (1 = off; typical sensitive: 10)</t>
@@ -760,7 +760,7 @@
     <t xml:space="preserve">html_report_v2_microdata</t>
   </si>
   <si>
-    <t xml:space="preserve">Embed the anonymised per-respondent microdata island in the v2 report (coded answer indices + weights — no names, IDs or text). TRUE powers the live filter, custom banners and COMPUTED views. Set FALSE for a confidentiality ship to insider populations (e.g. a small staff survey sent to the employer): the file then carries published aggregates only, and the live features + the Tracking tab switch off for that build. Tip: keep TRUE for your own working copy and build the client copy with FALSE from a second config.</t>
+    <t xml:space="preserve">Embed the anonymised per-respondent microdata island in the v2 report (coded answer indices + weights — no names, IDs or text). TRUE powers the live filter, custom banners and COMPUTED views. Set FALSE for a confidentiality ship to insider populations (e.g. a small staff survey sent to the employer): the file then carries published aggregates only, and the live features + the Tracking tab switch off for that build. FALSE is REQUIRED wherever min_reporting_base is a promise - with the island present, sub-k detail is reconstructable from the page source. Tip: keep TRUE for your own working copy and build the client copy with FALSE from a second config.</t>
   </si>
   <si>
     <t xml:space="preserve">sampling_note</t>

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="471">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -832,13 +832,22 @@
     <t xml:space="preserve">File path, or leave blank to auto-detect</t>
   </si>
   <si>
-    <t xml:space="preserve">PATTERNS TAB (OPTIONAL)</t>
+    <t xml:space="preserve">GROUP OVERVIEW TAB (OPTIONAL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patterns_banner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group overview tab: the banner group(s) to portray (label or id, comma-separated for more than one, e.g. 'Centre'). The tab is an overview of the SELECTED banner's groups - how many questions each sits ahead of and behind its peers on. Blank = every banner group is scanned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A banner label/id, or blank for all</t>
   </si>
   <si>
     <t xml:space="preserve">patterns_exclude_banners</t>
   </si>
   <si>
-    <t xml:space="preserve">Banners the Patterns tab must skip, comma-separated (label or code, e.g. Interviewer). Operational cuts are fieldwork QC, not client story — without this the tab's lead portrait can be an interviewer effect. The banner still works everywhere else (crosstabs, Differences); it just never becomes a portrait. Blank = scan every banner.</t>
+    <t xml:space="preserve">Banners the Group overview tab must skip, comma-separated (label or code, e.g. Interviewer). Operational cuts are fieldwork QC, not client story — without this the tab's lead portrait can be an interviewer effect. The banner still works everywhere else (crosstabs, Differences); it just never becomes a portrait. Blank = scan every banner.</t>
   </si>
   <si>
     <t xml:space="preserve">Comma-separated banner labels/codes, or leave blank</t>
@@ -847,7 +856,7 @@
     <t xml:space="preserve">patterns_headline</t>
   </si>
   <si>
-    <t xml:space="preserve">Pin the Patterns apex KPI tiles to these question codes, in order (e.g. Q78, Q79). Blank = auto-detect from question titles, which on a study with many section ratings can pick the wrong ones and crowd out the true headline.</t>
+    <t xml:space="preserve">Pin the Group overview apex KPI tiles to these question codes, in order (e.g. Q78, Q79). Blank = auto-detect from question titles, which on a study with many section ratings can pick the wrong ones and crowd out the true headline.</t>
   </si>
   <si>
     <t xml:space="preserve">Comma-separated question codes, or leave blank</t>
@@ -1102,15 +1111,9 @@
     <t xml:space="preserve">CategoryOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Theme</t>
-  </si>
-  <si>
     <t xml:space="preserve">KeyShare</t>
   </si>
   <si>
-    <t xml:space="preserve">AreaSummary</t>
-  </si>
-  <si>
     <t xml:space="preserve">BaseFilter</t>
   </si>
   <si>
@@ -1159,13 +1162,7 @@
     <t xml:space="preserve">[Optional] Order of the category in the report (1 = first). Set on any one question in the category; blank categories order by first appearance.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Theme/area label for the Patterns tab's area cards (often the same as Category). Questions sharing a Theme are scored together as an area. Blank = question joins no area.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Single/Multi questions only: the exact option, box or NET label whose share summarises this question for the Patterns tab - where a HIGHER share is BETTER (e.g. 'Always' on delivery day, 'Not a problem' on language). Blank = question stays out of the Patterns scan. Ignored on rated questions (their index is used).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Y marks THE question that summarises its Category/Theme area for the Patterns tab (the section-overall rating, e.g. 'satisfaction with the coolers overall'). The area then scores on this question; sibling questions become the explanation, not equal votes in an average. One per area.</t>
+    <t xml:space="preserve">[Optional] Single/Multi questions only: the exact option, box or NET label whose share summarises this question for the Group overview tab - where a HIGHER share is BETTER (e.g. 'Always' on delivery day, 'Not a problem' on language). Blank = question stays out of the Group overview scan. Ignored on rated questions (their index is used).</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] R expression to filter respondents (e.g. Q1 == "Male" or !is.na(Q20)). Leave blank for no filter.</t>
@@ -1189,22 +1186,16 @@
     <t xml:space="preserve">[Optional] Reference only - question wording for your convenience. Not used in processing.</t>
   </si>
   <si>
-    <t xml:space="preserve">Total</t>
+    <t xml:space="preserve">Q_Gender</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">Total sample (always include as first banner)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_Gender</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gender</t>
   </si>
   <si>
-    <t xml:space="preserve">Example: demographic banner question</t>
+    <t xml:space="preserve">Example: demographic banner question (Total is column 1 automatically - never add a Total row)</t>
   </si>
   <si>
     <t xml:space="preserve">Q_Satisfaction</t>
@@ -3721,34 +3712,34 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="s">
+      <c r="A114" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
+      <c r="B114" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C115" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="E115" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="A115" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
     </row>
     <row r="116">
       <c r="A116" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>32</v>
@@ -3757,37 +3748,37 @@
         <v>4</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E116" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
+      <c r="A117" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E117" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="B118" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C118" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="E118" s="14" t="s">
+      <c r="A118" s="9" t="s">
         <v>286</v>
       </c>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
     </row>
     <row r="119">
       <c r="A119" s="15" t="s">
@@ -3837,38 +3828,38 @@
         <v>294</v>
       </c>
       <c r="E121" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="E122" s="14" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-    </row>
     <row r="123">
-      <c r="A123" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="B123" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C123" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D123" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>229</v>
-      </c>
+      <c r="A123" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>36</v>
@@ -3877,10 +3868,10 @@
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
     </row>
     <row r="125">
@@ -3914,12 +3905,12 @@
         <v>305</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>36</v>
@@ -3928,10 +3919,10 @@
         <v>4</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>308</v>
+        <v>237</v>
       </c>
     </row>
     <row r="128">
@@ -3939,7 +3930,7 @@
         <v>309</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="C128" s="16" t="s">
         <v>4</v>
@@ -3952,37 +3943,37 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="s">
+      <c r="A129" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
+      <c r="B129" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E129" s="14" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="B130" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C130" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="E130" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="A130" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
     </row>
     <row r="131">
       <c r="A131" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>316</v>
+        <v>32</v>
       </c>
       <c r="C131" s="16" t="s">
         <v>4</v>
@@ -3991,34 +3982,34 @@
         <v>317</v>
       </c>
       <c r="E131" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="s">
+      <c r="B132" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
+      <c r="C132" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="B133" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C133" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="E133" s="14" t="s">
+      <c r="A133" s="9" t="s">
         <v>322</v>
       </c>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9"/>
     </row>
     <row r="134">
       <c r="A134" s="15" t="s">
@@ -4034,92 +4025,92 @@
         <v>324</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="s">
+      <c r="A135" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E135" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
     </row>
     <row r="136">
-      <c r="A136" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="B136" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="E136" s="14" t="s">
+      <c r="A136" s="9" t="s">
         <v>328</v>
       </c>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9"/>
+      <c r="E136" s="9"/>
     </row>
     <row r="137">
       <c r="A137" s="15" t="s">
         <v>329</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>330</v>
+        <v>36</v>
       </c>
       <c r="C137" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D137" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E137" s="14" t="s">
         <v>331</v>
-      </c>
-      <c r="E137" s="14" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="B138" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>334</v>
       </c>
       <c r="C138" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D138" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E138" s="14" t="s">
         <v>335</v>
-      </c>
-      <c r="E138" s="14" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B139" s="11" t="s">
         <v>337</v>
-      </c>
-      <c r="B139" s="11" t="s">
-        <v>338</v>
       </c>
       <c r="C139" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D139" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E139" s="14" t="s">
         <v>339</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B140" s="11" t="s">
         <v>341</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>338</v>
       </c>
       <c r="C140" s="16" t="s">
         <v>4</v>
@@ -4136,7 +4127,7 @@
         <v>344</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>36</v>
+        <v>341</v>
       </c>
       <c r="C141" s="16" t="s">
         <v>4</v>
@@ -4163,6 +4154,23 @@
       </c>
       <c r="E142" s="14" t="s">
         <v>349</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E143" s="14" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -4184,12 +4192,12 @@
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A132:E132"/>
-    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A136:E136"/>
   </mergeCells>
   <dataValidations count="18">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B28:B28">
@@ -4520,55 +4528,55 @@
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B115:B115</xm:sqref>
+          <xm:sqref>B116:B116</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B116:B116</xm:sqref>
+          <xm:sqref>B117:B117</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B128:B128</xm:sqref>
+          <xm:sqref>B129:B129</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B130:B130</xm:sqref>
+          <xm:sqref>B131:B131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
           </x14:formula1>
-          <xm:sqref>B131:B131</xm:sqref>
+          <xm:sqref>B132:B132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B137:B137</xm:sqref>
+          <xm:sqref>B138:B138</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B138:B138</xm:sqref>
+          <xm:sqref>B139:B139</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B139:B139</xm:sqref>
+          <xm:sqref>B140:B140</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B140:B140</xm:sqref>
+          <xm:sqref>B141:B141</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4590,168 +4598,154 @@
     <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="20.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="22.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="13.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="35.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="30.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="22.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="35.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="30.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="22.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="16.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="14.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="16.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="40.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="R4" s="13" t="s">
         <v>388</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>390</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>391</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>125</v>
       </c>
       <c r="D5" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>391</v>
-      </c>
       <c r="H5" s="17" t="s">
         <v>36</v>
       </c>
@@ -4780,12 +4774,6 @@
         <v>36</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S5" s="17" t="s">
         <v>392</v>
       </c>
     </row>
@@ -4794,102 +4782,96 @@
         <v>393</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>391</v>
+        <v>125</v>
       </c>
       <c r="C6" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="H6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" s="17" t="s">
         <v>394</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S6" s="17" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>36</v>
-      </c>
       <c r="N7" s="17" t="s">
-        <v>36</v>
+        <v>393</v>
       </c>
       <c r="O7" s="17" t="s">
         <v>36</v>
@@ -4898,12 +4880,6 @@
         <v>36</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="R7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S7" s="17" t="s">
         <v>397</v>
       </c>
     </row>
@@ -4912,10 +4888,10 @@
         <v>398</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>391</v>
+        <v>125</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>36</v>
@@ -4927,7 +4903,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>36</v>
@@ -4945,85 +4921,39 @@
         <v>36</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>36</v>
+        <v>399</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>36</v>
+        <v>398</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S8" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="P9" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="R9" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="S9" s="17" t="s">
-        <v>404</v>
-      </c>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -5043,8 +4973,6 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -5064,8 +4992,6 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -5085,8 +5011,6 @@
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -5106,8 +5030,6 @@
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -5127,8 +5049,6 @@
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -5148,8 +5068,6 @@
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -5169,8 +5087,6 @@
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -5190,8 +5106,6 @@
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -5211,8 +5125,6 @@
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -5232,8 +5144,6 @@
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -5253,8 +5163,6 @@
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
@@ -5274,8 +5182,6 @@
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
@@ -5295,8 +5201,6 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
@@ -5316,8 +5220,6 @@
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
@@ -5337,8 +5239,6 @@
       <c r="O24" s="11"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
@@ -5358,8 +5258,6 @@
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
@@ -5379,8 +5277,6 @@
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
@@ -5400,8 +5296,6 @@
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
-      <c r="S27" s="11"/>
     </row>
     <row r="28">
       <c r="A28" s="11"/>
@@ -5421,8 +5315,6 @@
       <c r="O28" s="11"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
     </row>
     <row r="29">
       <c r="A29" s="11"/>
@@ -5442,8 +5334,6 @@
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
@@ -5463,8 +5353,6 @@
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
     </row>
     <row r="31">
       <c r="A31" s="11"/>
@@ -5484,8 +5372,6 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
-      <c r="R31" s="11"/>
-      <c r="S31" s="11"/>
     </row>
     <row r="32">
       <c r="A32" s="11"/>
@@ -5505,8 +5391,6 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
     </row>
     <row r="33">
       <c r="A33" s="11"/>
@@ -5526,8 +5410,6 @@
       <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
     </row>
     <row r="34">
       <c r="A34" s="11"/>
@@ -5547,8 +5429,6 @@
       <c r="O34" s="11"/>
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
     </row>
     <row r="35">
       <c r="A35" s="11"/>
@@ -5568,8 +5448,6 @@
       <c r="O35" s="11"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
     </row>
     <row r="36">
       <c r="A36" s="11"/>
@@ -5589,8 +5467,6 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
     </row>
     <row r="37">
       <c r="A37" s="11"/>
@@ -5610,8 +5486,6 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="11"/>
     </row>
     <row r="38">
       <c r="A38" s="11"/>
@@ -5631,8 +5505,6 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
-      <c r="R38" s="11"/>
-      <c r="S38" s="11"/>
     </row>
     <row r="39">
       <c r="A39" s="11"/>
@@ -5652,8 +5524,6 @@
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
-      <c r="R39" s="11"/>
-      <c r="S39" s="11"/>
     </row>
     <row r="40">
       <c r="A40" s="11"/>
@@ -5673,8 +5543,6 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
-      <c r="S40" s="11"/>
     </row>
     <row r="41">
       <c r="A41" s="11"/>
@@ -5694,8 +5562,6 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
     </row>
     <row r="42">
       <c r="A42" s="11"/>
@@ -5715,8 +5581,6 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="11"/>
     </row>
     <row r="43">
       <c r="A43" s="11"/>
@@ -5736,8 +5600,6 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
     </row>
     <row r="44">
       <c r="A44" s="11"/>
@@ -5757,8 +5619,6 @@
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="11"/>
     </row>
     <row r="45">
       <c r="A45" s="11"/>
@@ -5778,8 +5638,6 @@
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
     </row>
     <row r="46">
       <c r="A46" s="11"/>
@@ -5799,8 +5657,6 @@
       <c r="O46" s="11"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
     </row>
     <row r="47">
       <c r="A47" s="11"/>
@@ -5820,8 +5676,6 @@
       <c r="O47" s="11"/>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
-      <c r="R47" s="11"/>
-      <c r="S47" s="11"/>
     </row>
     <row r="48">
       <c r="A48" s="11"/>
@@ -5841,8 +5695,6 @@
       <c r="O48" s="11"/>
       <c r="P48" s="11"/>
       <c r="Q48" s="11"/>
-      <c r="R48" s="11"/>
-      <c r="S48" s="11"/>
     </row>
     <row r="49">
       <c r="A49" s="11"/>
@@ -5862,8 +5714,6 @@
       <c r="O49" s="11"/>
       <c r="P49" s="11"/>
       <c r="Q49" s="11"/>
-      <c r="R49" s="11"/>
-      <c r="S49" s="11"/>
     </row>
     <row r="50">
       <c r="A50" s="11"/>
@@ -5883,8 +5733,6 @@
       <c r="O50" s="11"/>
       <c r="P50" s="11"/>
       <c r="Q50" s="11"/>
-      <c r="R50" s="11"/>
-      <c r="S50" s="11"/>
     </row>
     <row r="51">
       <c r="A51" s="11"/>
@@ -5904,8 +5752,6 @@
       <c r="O51" s="11"/>
       <c r="P51" s="11"/>
       <c r="Q51" s="11"/>
-      <c r="R51" s="11"/>
-      <c r="S51" s="11"/>
     </row>
     <row r="52">
       <c r="A52" s="11"/>
@@ -5925,8 +5771,6 @@
       <c r="O52" s="11"/>
       <c r="P52" s="11"/>
       <c r="Q52" s="11"/>
-      <c r="R52" s="11"/>
-      <c r="S52" s="11"/>
     </row>
     <row r="53">
       <c r="A53" s="11"/>
@@ -5946,8 +5790,6 @@
       <c r="O53" s="11"/>
       <c r="P53" s="11"/>
       <c r="Q53" s="11"/>
-      <c r="R53" s="11"/>
-      <c r="S53" s="11"/>
     </row>
     <row r="54">
       <c r="A54" s="11"/>
@@ -5967,8 +5809,6 @@
       <c r="O54" s="11"/>
       <c r="P54" s="11"/>
       <c r="Q54" s="11"/>
-      <c r="R54" s="11"/>
-      <c r="S54" s="11"/>
     </row>
     <row r="55">
       <c r="A55" s="11"/>
@@ -5988,8 +5828,6 @@
       <c r="O55" s="11"/>
       <c r="P55" s="11"/>
       <c r="Q55" s="11"/>
-      <c r="R55" s="11"/>
-      <c r="S55" s="11"/>
     </row>
     <row r="56">
       <c r="A56" s="11"/>
@@ -6009,8 +5847,6 @@
       <c r="O56" s="11"/>
       <c r="P56" s="11"/>
       <c r="Q56" s="11"/>
-      <c r="R56" s="11"/>
-      <c r="S56" s="11"/>
     </row>
     <row r="57">
       <c r="A57" s="11"/>
@@ -6030,8 +5866,6 @@
       <c r="O57" s="11"/>
       <c r="P57" s="11"/>
       <c r="Q57" s="11"/>
-      <c r="R57" s="11"/>
-      <c r="S57" s="11"/>
     </row>
     <row r="58">
       <c r="A58" s="11"/>
@@ -6051,41 +5885,18 @@
       <c r="O58" s="11"/>
       <c r="P58" s="11"/>
       <c r="Q58" s="11"/>
-      <c r="R58" s="11"/>
-      <c r="S58" s="11"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="11"/>
-      <c r="Q59" s="11"/>
-      <c r="R59" s="11"/>
-      <c r="S59" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F59">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F58">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I59">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I58">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -6094,36 +5905,30 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B5:B59</xm:sqref>
+          <xm:sqref>B5:B58</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>C5:C59</xm:sqref>
+          <xm:sqref>C5:C58</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>D5:D59</xm:sqref>
+          <xm:sqref>D5:D58</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>G5:G59</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
-          </x14:formula1>
-          <xm:sqref>L5:L59</xm:sqref>
+          <xm:sqref>G5:G58</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6143,122 +5948,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -6284,48 +6089,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>442</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -6336,10 +6141,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>36</v>
@@ -6350,16 +6155,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6564,42 +6369,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6607,10 +6412,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6744,56 +6549,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -563,12 +563,6 @@
   </si>
   <si>
     <t xml:space="preserve">HTML REPORT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">html_report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate an interactive HTML report in addition to the Excel output.</t>
   </si>
   <si>
     <t xml:space="preserve">brand_colour</t>
@@ -3137,67 +3131,67 @@
         <v>182</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="s">
-        <v>188</v>
+      <c r="A81" s="15" t="s">
+        <v>190</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="C81" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>4</v>
-      </c>
       <c r="D82" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83">
@@ -3205,38 +3199,38 @@
         <v>195</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="s">
-        <v>197</v>
+      <c r="A84" s="15" t="s">
+        <v>199</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>36</v>
@@ -3245,15 +3239,15 @@
         <v>4</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>36</v>
@@ -3262,15 +3256,15 @@
         <v>4</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>36</v>
@@ -3279,15 +3273,15 @@
         <v>4</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>36</v>
@@ -3296,15 +3290,15 @@
         <v>4</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>36</v>
@@ -3313,15 +3307,15 @@
         <v>4</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>36</v>
@@ -3330,15 +3324,15 @@
         <v>4</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>36</v>
@@ -3347,78 +3341,78 @@
         <v>4</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="s">
-        <v>222</v>
+      <c r="A92" s="10" t="s">
+        <v>223</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C92" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C93" s="16" t="s">
         <v>4</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>15</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>226</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>34</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="s">
+      <c r="A94" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E94" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="B94" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C94" s="16" t="s">
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95" s="16" t="s">
         <v>4</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>15</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>232</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96">
@@ -3435,12 +3429,12 @@
         <v>234</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>36</v>
@@ -3449,10 +3443,10 @@
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="98">
@@ -3469,41 +3463,41 @@
         <v>239</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C99" s="16" t="s">
+      <c r="A99" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C100" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="E99" s="14" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="s">
+      <c r="D100" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
+      <c r="E100" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="s">
         <v>244</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C101" s="16" t="s">
         <v>4</v>
@@ -3520,7 +3514,7 @@
         <v>246</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C102" s="16" t="s">
         <v>4</v>
@@ -3529,46 +3523,46 @@
         <v>247</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>34</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="C103" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>252</v>
+        <v>36</v>
       </c>
       <c r="C104" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>36</v>
@@ -3577,10 +3571,10 @@
         <v>4</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106">
@@ -3588,7 +3582,7 @@
         <v>258</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C106" s="16" t="s">
         <v>4</v>
@@ -3597,7 +3591,7 @@
         <v>259</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107">
@@ -3605,7 +3599,7 @@
         <v>260</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C107" s="16" t="s">
         <v>4</v>
@@ -3614,12 +3608,12 @@
         <v>261</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>34</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>36</v>
@@ -3628,15 +3622,15 @@
         <v>4</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>36</v>
@@ -3645,41 +3639,41 @@
         <v>4</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C110" s="16" t="s">
+      <c r="A110" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C111" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="E110" s="14" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="s">
+      <c r="D111" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
+      <c r="E111" s="14" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>36</v>
@@ -3688,15 +3682,15 @@
         <v>4</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>36</v>
@@ -3705,37 +3699,37 @@
         <v>4</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C114" s="16" t="s">
+      <c r="A114" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="E114" s="14" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="s">
+      <c r="D115" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="9"/>
+      <c r="E115" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="s">
@@ -3755,34 +3749,34 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="15" t="s">
+      <c r="A117" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B117" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C117" s="16" t="s">
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="E117" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="s">
+      <c r="D118" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
+      <c r="E118" s="14" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>36</v>
@@ -3791,15 +3785,15 @@
         <v>4</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>36</v>
@@ -3808,15 +3802,15 @@
         <v>4</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>36</v>
@@ -3825,37 +3819,37 @@
         <v>4</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>295</v>
+        <v>227</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="s">
+      <c r="A122" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B122" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C122" s="16" t="s">
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C123" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="E122" s="14" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="s">
+      <c r="D123" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
+      <c r="E123" s="14" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
@@ -3871,12 +3865,12 @@
         <v>300</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>229</v>
+        <v>301</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>36</v>
@@ -3885,15 +3879,15 @@
         <v>4</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>36</v>
@@ -3902,10 +3896,10 @@
         <v>4</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>306</v>
+        <v>235</v>
       </c>
     </row>
     <row r="127">
@@ -3922,98 +3916,98 @@
         <v>308</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>237</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="C128" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="B129" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C129" s="16" t="s">
+      <c r="A129" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C130" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="E129" s="14" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="s">
+      <c r="D130" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
+      <c r="E130" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="15" t="s">
         <v>316</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>32</v>
+        <v>317</v>
       </c>
       <c r="C131" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>34</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="C132" s="16" t="s">
+      <c r="A132" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C133" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="9" t="s">
+      <c r="D133" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
+      <c r="E133" s="14" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>36</v>
@@ -4022,126 +4016,126 @@
         <v>4</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="15" t="s">
+      <c r="A135" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B135" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C135" s="16" t="s">
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9"/>
+      <c r="E135" s="9"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C136" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="E135" s="14" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="9" t="s">
+      <c r="D136" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
+      <c r="E136" s="14" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>36</v>
+        <v>331</v>
       </c>
       <c r="C137" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E137" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C138" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C139" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C140" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="C141" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>36</v>
@@ -4150,27 +4144,10 @@
         <v>4</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="15" t="s">
         <v>350</v>
-      </c>
-      <c r="B143" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C143" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="E143" s="14" t="s">
-        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -4190,14 +4167,14 @@
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A67:E67"/>
     <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A130:E130"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A135:E135"/>
   </mergeCells>
   <dataValidations count="18">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B28:B28">
@@ -4277,7 +4254,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="50">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="49">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx,csv"</xm:f>
@@ -4484,21 +4461,21 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B79:B79</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>"warm,cool,research,teal,red,brand"</xm:f>
           </x14:formula1>
-          <xm:sqref>B84:B84</xm:sqref>
+          <xm:sqref>B83:B83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B93:B93</xm:sqref>
+          <xm:sqref>B92:B92</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B100:B100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4508,21 +4485,21 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B102:B102</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
           </x14:formula1>
-          <xm:sqref>B104:B104</xm:sqref>
+          <xm:sqref>B103:B103</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B107:B107</xm:sqref>
+          <xm:sqref>B106:B106</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"FALSE,TRUE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B115:B115</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4532,51 +4509,45 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"FALSE,TRUE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B117:B117</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B129:B129</xm:sqref>
+          <xm:sqref>B128:B128</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B131:B131</xm:sqref>
+          <xm:sqref>B130:B130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
           </x14:formula1>
-          <xm:sqref>B132:B132</xm:sqref>
+          <xm:sqref>B131:B131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B138:B138</xm:sqref>
+          <xm:sqref>B137:B137</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B139:B139</xm:sqref>
+          <xm:sqref>B138:B138</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B140:B140</xm:sqref>
+          <xm:sqref>B139:B139</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B141:B141</xm:sqref>
+          <xm:sqref>B140:B140</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4610,182 +4581,182 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>369</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="I4" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="J4" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="K4" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="L4" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="M4" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="N4" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="O4" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="P4" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="Q4" s="13" t="s">
         <v>386</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q4" s="13" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>125</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="17" t="s">
         <v>390</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>125</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>36</v>
@@ -4827,71 +4798,71 @@
         <v>36</v>
       </c>
       <c r="Q6" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>395</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="P7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>125</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>36</v>
@@ -4903,7 +4874,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>36</v>
@@ -4921,19 +4892,19 @@
         <v>36</v>
       </c>
       <c r="M8" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="O8" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q8" s="17" t="s">
         <v>399</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="P8" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -5948,122 +5919,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>404</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>407</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>410</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>413</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>416</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>419</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>422</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>425</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>428</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>431</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -6089,48 +6060,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>436</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>440</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -6141,10 +6112,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>36</v>
@@ -6155,16 +6126,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6369,42 +6340,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>451</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>454</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6412,10 +6383,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6549,56 +6520,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>465</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -103,10 +103,7 @@
     <t xml:space="preserve">xlsx</t>
   </si>
   <si>
-    <t xml:space="preserve">Output file format: Excel workbook or separate CSV files.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xlsx or csv</t>
+    <t xml:space="preserve">Output file format. Excel workbook is the only writer.</t>
   </si>
   <si>
     <t xml:space="preserve">WEIGHTING</t>
@@ -2063,12 +2060,12 @@
         <v>28</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2077,109 +2074,109 @@
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2188,126 +2185,126 @@
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2316,24 +2313,24 @@
     </row>
     <row r="27">
       <c r="A27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>0</v>
@@ -2342,15 +2339,15 @@
         <v>15</v>
       </c>
       <c r="D28" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>71</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>1</v>
@@ -2359,15 +2356,15 @@
         <v>15</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>1</v>
@@ -2376,15 +2373,15 @@
         <v>15</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>1</v>
@@ -2393,15 +2390,15 @@
         <v>15</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -2410,58 +2407,58 @@
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -2470,24 +2467,24 @@
     </row>
     <row r="37">
       <c r="A37" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>0.05</v>
@@ -2496,15 +2493,15 @@
         <v>15</v>
       </c>
       <c r="D38" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>30</v>
@@ -2513,15 +2510,15 @@
         <v>15</v>
       </c>
       <c r="D39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="14" t="s">
         <v>93</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B40" s="11" t="n">
         <v>1</v>
@@ -2530,100 +2527,100 @@
         <v>4</v>
       </c>
       <c r="D40" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -2632,92 +2629,92 @@
     </row>
     <row r="47">
       <c r="A47" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2726,75 +2723,75 @@
     </row>
     <row r="53">
       <c r="A53" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>125</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="14" t="s">
         <v>126</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B57" s="11" t="n">
         <v>1</v>
@@ -2803,15 +2800,15 @@
         <v>15</v>
       </c>
       <c r="D57" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -2820,24 +2817,24 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -2846,24 +2843,24 @@
     </row>
     <row r="61">
       <c r="A61" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -2872,75 +2869,75 @@
     </row>
     <row r="63">
       <c r="A63" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D64" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" s="14" t="s">
         <v>147</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E65" s="14" t="s">
         <v>151</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>154</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E66" s="14" t="s">
         <v>155</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -2949,7 +2946,7 @@
     </row>
     <row r="68">
       <c r="A68" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B68" s="11" t="n">
         <v>10</v>
@@ -2958,15 +2955,15 @@
         <v>15</v>
       </c>
       <c r="D68" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B69" s="11" t="n">
         <v>10</v>
@@ -2975,15 +2972,15 @@
         <v>15</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B70" s="11" t="n">
         <v>30</v>
@@ -2992,15 +2989,15 @@
         <v>15</v>
       </c>
       <c r="D70" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E70" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B71" s="11" t="n">
         <v>0</v>
@@ -3009,15 +3006,15 @@
         <v>15</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
@@ -3026,15 +3023,15 @@
         <v>15</v>
       </c>
       <c r="D72" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="14" t="s">
         <v>169</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B73" s="11" t="n">
         <v>5</v>
@@ -3043,15 +3040,15 @@
         <v>15</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B74" s="11" t="n">
         <v>7</v>
@@ -3060,15 +3057,15 @@
         <v>15</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B75" s="11" t="n">
         <v>5</v>
@@ -3077,15 +3074,15 @@
         <v>15</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B76" s="11" t="n">
         <v>60</v>
@@ -3094,15 +3091,15 @@
         <v>15</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B77" s="11" t="n">
         <v>40</v>
@@ -3111,15 +3108,15 @@
         <v>15</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -3128,347 +3125,347 @@
     </row>
     <row r="79">
       <c r="A79" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B79" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E79" s="14" t="s">
         <v>184</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B80" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>187</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E80" s="14" t="s">
         <v>188</v>
-      </c>
-      <c r="E80" s="14" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C81" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D81" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E81" s="14" t="s">
         <v>191</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B83" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="E83" s="14" t="s">
         <v>197</v>
-      </c>
-      <c r="E83" s="14" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C84" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D84" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="E84" s="14" t="s">
         <v>200</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C85" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E85" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C86" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D86" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E86" s="14" t="s">
         <v>206</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D87" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E87" s="14" t="s">
         <v>209</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C88" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D88" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="E88" s="14" t="s">
         <v>212</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C89" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D89" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="E89" s="14" t="s">
         <v>215</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C90" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D90" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E90" s="14" t="s">
         <v>218</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C91" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D91" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E91" s="14" t="s">
         <v>221</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C93" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D93" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E93" s="14" t="s">
         <v>226</v>
-      </c>
-      <c r="E93" s="14" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B94" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>229</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C95" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C96" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D96" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E96" s="14" t="s">
         <v>234</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C97" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C98" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D98" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="E98" s="14" t="s">
         <v>239</v>
-      </c>
-      <c r="E98" s="14" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
@@ -3477,177 +3474,177 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C100" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C101" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C102" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D102" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E102" s="14" t="s">
         <v>247</v>
-      </c>
-      <c r="E102" s="14" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B103" s="11" t="s">
         <v>249</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>250</v>
       </c>
       <c r="C103" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D103" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E103" s="14" t="s">
         <v>251</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C104" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D104" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E104" s="14" t="s">
         <v>254</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C105" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C106" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C107" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D107" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E107" s="14" t="s">
         <v>261</v>
-      </c>
-      <c r="E107" s="14" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C108" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D108" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E108" s="14" t="s">
         <v>264</v>
-      </c>
-      <c r="E108" s="14" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C109" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D109" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="E109" s="14" t="s">
         <v>267</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
@@ -3656,58 +3653,58 @@
     </row>
     <row r="111">
       <c r="A111" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C111" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D111" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E111" s="14" t="s">
         <v>271</v>
-      </c>
-      <c r="E111" s="14" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C112" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D112" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E112" s="14" t="s">
         <v>274</v>
-      </c>
-      <c r="E112" s="14" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C113" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D113" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E113" s="14" t="s">
         <v>277</v>
-      </c>
-      <c r="E113" s="14" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -3716,41 +3713,41 @@
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C115" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C116" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -3759,75 +3756,75 @@
     </row>
     <row r="118">
       <c r="A118" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C118" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E118" s="14" t="s">
         <v>286</v>
-      </c>
-      <c r="E118" s="14" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C119" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D119" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="E119" s="14" t="s">
         <v>289</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C120" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D120" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E120" s="14" t="s">
         <v>292</v>
-      </c>
-      <c r="E120" s="14" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C121" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -3836,109 +3833,109 @@
     </row>
     <row r="123">
       <c r="A123" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C123" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C124" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="E124" s="14" t="s">
         <v>300</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C125" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D125" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="E125" s="14" t="s">
         <v>303</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C126" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C127" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D127" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="E127" s="14" t="s">
         <v>308</v>
-      </c>
-      <c r="E127" s="14" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C128" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D128" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="E128" s="14" t="s">
         <v>311</v>
-      </c>
-      <c r="E128" s="14" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -3947,41 +3944,41 @@
     </row>
     <row r="130">
       <c r="A130" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C130" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="B131" s="11" t="s">
         <v>316</v>
-      </c>
-      <c r="B131" s="11" t="s">
-        <v>317</v>
       </c>
       <c r="C131" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D131" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="E131" s="14" t="s">
         <v>318</v>
-      </c>
-      <c r="E131" s="14" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
@@ -3990,41 +3987,41 @@
     </row>
     <row r="133">
       <c r="A133" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C133" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D133" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E133" s="14" t="s">
         <v>322</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C134" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -4033,121 +4030,121 @@
     </row>
     <row r="136">
       <c r="A136" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C136" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D136" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E136" s="14" t="s">
         <v>328</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B137" s="11" t="s">
         <v>330</v>
-      </c>
-      <c r="B137" s="11" t="s">
-        <v>331</v>
       </c>
       <c r="C137" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D137" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E137" s="14" t="s">
         <v>332</v>
-      </c>
-      <c r="E137" s="14" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B138" s="11" t="s">
         <v>334</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>335</v>
       </c>
       <c r="C138" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D138" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="E138" s="14" t="s">
         <v>336</v>
-      </c>
-      <c r="E138" s="14" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="B139" s="11" t="s">
         <v>338</v>
-      </c>
-      <c r="B139" s="11" t="s">
-        <v>339</v>
       </c>
       <c r="C139" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D139" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E139" s="14" t="s">
         <v>340</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C140" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D140" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E140" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="E140" s="14" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C141" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D141" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="E141" s="14" t="s">
         <v>346</v>
-      </c>
-      <c r="E141" s="14" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C142" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D142" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E142" s="14" t="s">
         <v>349</v>
-      </c>
-      <c r="E142" s="14" t="s">
-        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4257,7 +4254,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="49">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"xlsx,csv"</xm:f>
+            <xm:f>"xlsx"</xm:f>
           </x14:formula1>
           <xm:sqref>B10:B10</xm:sqref>
         </x14:dataValidation>
@@ -4581,330 +4578,330 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>368</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="I4" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="J4" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="K4" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="L4" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="M4" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="N4" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="O4" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="P4" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="Q4" s="13" t="s">
         <v>385</v>
-      </c>
-      <c r="Q4" s="13" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>388</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>389</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="17" t="s">
         <v>391</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="17" t="s">
+      <c r="N7" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>394</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="P7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="17" t="s">
+      <c r="N8" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="O8" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="N8" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="O8" s="17" t="s">
+      <c r="P8" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q8" s="17" t="s">
         <v>398</v>
-      </c>
-      <c r="P8" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -5919,122 +5916,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>403</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>406</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="14" t="s">
         <v>409</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="14" t="s">
         <v>412</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="14" t="s">
         <v>415</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>418</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="14" t="s">
         <v>421</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="14" t="s">
         <v>424</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="14" t="s">
         <v>427</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="C13" s="14" t="s">
         <v>430</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -6060,82 +6057,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>435</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>439</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>442</v>
-      </c>
       <c r="C5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>444</v>
-      </c>
       <c r="C6" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>445</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6340,42 +6337,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>450</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>453</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>455</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>456</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6383,10 +6380,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>457</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>458</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6520,56 +6517,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>462</v>
-      </c>
       <c r="C3" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>463</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>464</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -205,12 +205,6 @@
     <t xml:space="preserve">Show standard deviation for Rating/Likert mean scores.</t>
   </si>
   <si>
-    <t xml:space="preserve">show_charts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include inline SVG charts in HTML report output.</t>
-  </si>
-  <si>
     <t xml:space="preserve">DECIMAL PLACES</t>
   </si>
   <si>
@@ -448,12 +442,6 @@
     <t xml:space="preserve">SUMMARY DASHBOARD</t>
   </si>
   <si>
-    <t xml:space="preserve">include_summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include a visual summary dashboard in HTML report with gauge charts.</t>
-  </si>
-  <si>
     <t xml:space="preserve">fieldwork_dates</t>
   </si>
   <si>
@@ -463,30 +451,6 @@
     <t xml:space="preserve">e.g. January - March 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">dashboard_metrics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NET POSITIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metric types to display in dashboard gauges. Comma-separated for multiple: NET POSITIVE, MEAN, NPS, INDEX, or custom box-category label.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NET POSITIVE, MEAN, NPS, INDEX, or custom label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dashboard_sort_gauges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort order for dashboard gauge charts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">desc, asc, or alphabetic</t>
-  </si>
-  <si>
     <t xml:space="preserve">DASHBOARD COLOUR THRESHOLDS (RAG)</t>
   </si>
   <si>
@@ -505,21 +469,6 @@
     <t xml:space="preserve">Scale maximum for index values in dashboard.</t>
   </si>
   <si>
-    <t xml:space="preserve">dashboard_green_net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NET POSITIVE &gt;= this value shows GREEN (good performance).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 to 100 (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dashboard_amber_net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NET POSITIVE &gt;= this value (but &lt; green) shows AMBER. Below = RED.</t>
-  </si>
-  <si>
     <t xml:space="preserve">dashboard_green_mean</t>
   </si>
   <si>
@@ -547,18 +496,6 @@
     <t xml:space="preserve">Index score &gt;= this value (but &lt; green) shows AMBER. Below = RED.</t>
   </si>
   <si>
-    <t xml:space="preserve">dashboard_green_custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom metric &gt;= this value shows GREEN.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dashboard_amber_custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom metric &gt;= this value (but &lt; green) shows AMBER. Below = RED.</t>
-  </si>
-  <si>
     <t xml:space="preserve">HTML REPORT</t>
   </si>
   <si>
@@ -685,12 +622,6 @@
     <t xml:space="preserve">Hex colour code (e.g. #D4918E)</t>
   </si>
   <si>
-    <t xml:space="preserve">embed_frequencies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include frequency data (counts) in the HTML report tables.</t>
-  </si>
-  <si>
     <t xml:space="preserve">project_title</t>
   </si>
   <si>
@@ -869,39 +800,6 @@
   </si>
   <si>
     <t xml:space="preserve">ROW DESCRIPTORS (HTML Report)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">index_descriptor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explanatory label shown below Index score rows in HTML crosstabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e.g. Weighted mean on 0-10 scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_descriptor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explanatory label shown below Mean score rows in HTML crosstabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e.g. Average rating (1-5 scale)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nps_descriptor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explanatory label shown below NPS score rows in HTML crosstabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e.g. Promoters minus Detractors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">priority_metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metric to highlight in the report (used for visual emphasis).</t>
   </si>
   <si>
     <t xml:space="preserve">ANALYST &amp; CLOSING SECTION</t>
@@ -2286,63 +2184,63 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="12" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="D26" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
@@ -2359,7 +2257,7 @@
         <v>73</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -2376,41 +2274,41 @@
         <v>75</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="12" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="s">
+      <c r="D32" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="E32" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>15</v>
@@ -2427,7 +2325,7 @@
         <v>81</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>15</v>
@@ -2440,37 +2338,37 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="12" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="14" t="s">
+      <c r="D36" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>39</v>
+      <c r="B37" s="11" t="n">
+        <v>0.05</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>15</v>
@@ -2479,69 +2377,69 @@
         <v>87</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="11" t="n">
-        <v>0.05</v>
+        <v>30</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="s">
-        <v>91</v>
+      <c r="A39" s="15" t="s">
+        <v>92</v>
       </c>
       <c r="B39" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C39" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="16" t="s">
+      <c r="D40" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>4</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>15</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>98</v>
@@ -2572,7 +2470,7 @@
         <v>101</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>4</v>
@@ -2581,51 +2479,51 @@
         <v>102</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="13" t="s">
+      <c r="A45" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="s">
+      <c r="B46" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
+      <c r="E46" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="s">
@@ -2649,7 +2547,7 @@
         <v>113</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>15</v>
@@ -2666,7 +2564,7 @@
         <v>115</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>15</v>
@@ -2683,59 +2581,59 @@
         <v>117</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E50" s="14" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="11" t="s">
+      <c r="A51" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
+      <c r="D52" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54">
@@ -2743,7 +2641,7 @@
         <v>127</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>15</v>
@@ -2752,7 +2650,7 @@
         <v>128</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55">
@@ -2760,7 +2658,7 @@
         <v>129</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>15</v>
@@ -2769,15 +2667,15 @@
         <v>130</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B56" s="11" t="s">
-        <v>124</v>
+      <c r="B56" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>15</v>
@@ -2786,113 +2684,105 @@
         <v>132</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="12" t="s">
+      <c r="A57" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="16" t="s">
+      <c r="D60" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C61" s="12" t="s">
+      <c r="D62" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>4</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>146</v>
@@ -2905,170 +2795,170 @@
       <c r="A65" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B65" s="11" t="s">
-        <v>149</v>
+      <c r="B65" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>7</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="E66" s="14" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
+      <c r="E67" s="14" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B68" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B69" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E69" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="B70" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>164</v>
-      </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="B71" s="11" t="n">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B72" s="11" t="n">
-        <v>7</v>
+        <v>164</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>165</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="B73" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="13" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="s">
+      <c r="E73" s="14" t="s">
         <v>170</v>
-      </c>
-      <c r="B73" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B74" s="11" t="n">
-        <v>7</v>
+        <v>171</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B75" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="B75" s="11" t="n">
-        <v>5</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>15</v>
@@ -3077,89 +2967,97 @@
         <v>175</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B76" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>15</v>
+      <c r="A76" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B77" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>15</v>
+      <c r="A77" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
+      <c r="A78" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="s">
-        <v>181</v>
+      <c r="A79" s="15" t="s">
+        <v>186</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="s">
-        <v>185</v>
+      <c r="A80" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>35</v>
@@ -3168,49 +3066,49 @@
         <v>4</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="s">
-        <v>192</v>
+      <c r="A82" s="15" t="s">
+        <v>195</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="s">
-        <v>194</v>
+      <c r="A83" s="15" t="s">
+        <v>198</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>35</v>
@@ -3219,24 +3117,24 @@
         <v>4</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="15" t="s">
-        <v>201</v>
+      <c r="A85" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C85" s="16" t="s">
-        <v>4</v>
+        <v>205</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E85" s="14" t="s">
         <v>203</v>
@@ -3244,7 +3142,7 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>35</v>
@@ -3253,15 +3151,15 @@
         <v>4</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>35</v>
@@ -3270,15 +3168,15 @@
         <v>4</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>35</v>
@@ -3287,15 +3185,15 @@
         <v>4</v>
       </c>
       <c r="D88" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="E88" s="14" t="s">
         <v>211</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>35</v>
@@ -3304,58 +3202,50 @@
         <v>4</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C90" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D90" s="13" t="s">
+      <c r="A90" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E90" s="14" t="s">
-        <v>218</v>
-      </c>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
     </row>
     <row r="91">
       <c r="A91" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C91" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D91" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="s">
         <v>220</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="s">
-        <v>222</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>15</v>
+      <c r="C92" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E92" s="14" t="s">
         <v>33</v>
@@ -3363,7 +3253,7 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>35</v>
@@ -3372,32 +3262,32 @@
         <v>4</v>
       </c>
       <c r="D93" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="E93" s="14" t="s">
+      <c r="B94" s="11" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="s">
+      <c r="C94" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="E94" s="14" t="s">
         <v>228</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>35</v>
@@ -3406,10 +3296,10 @@
         <v>4</v>
       </c>
       <c r="D95" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E95" s="14" t="s">
         <v>231</v>
-      </c>
-      <c r="E95" s="14" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="96">
@@ -3426,29 +3316,29 @@
         <v>233</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C97" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>234</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>35</v>
@@ -3457,58 +3347,58 @@
         <v>4</v>
       </c>
       <c r="D98" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E98" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="E98" s="14" t="s">
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="s">
+      <c r="B99" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D99" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
+      <c r="E99" s="14" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C100" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>33</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C101" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="A101" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
     </row>
     <row r="102">
       <c r="A102" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>35</v>
@@ -3517,18 +3407,18 @@
         <v>4</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>249</v>
+        <v>35</v>
       </c>
       <c r="C103" s="16" t="s">
         <v>4</v>
@@ -3558,25 +3448,17 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="15" t="s">
+      <c r="A105" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B105" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C105" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>247</v>
-      </c>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>31</v>
@@ -3585,7 +3467,7 @@
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>33</v>
@@ -3593,67 +3475,59 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C107" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D107" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="E107" s="14" t="s">
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="s">
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="B108" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C108" s="16" t="s">
+      <c r="B110" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C110" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="13" t="s">
+      <c r="D110" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="E108" s="14" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="B109" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C109" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="B110" s="9"/>
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
+      <c r="E110" s="14" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="15" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>35</v>
@@ -3662,15 +3536,15 @@
         <v>4</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>35</v>
@@ -3679,15 +3553,15 @@
         <v>4</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>35</v>
@@ -3696,101 +3570,101 @@
         <v>4</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>277</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
+      <c r="A114" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="C115" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E115" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D117" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="E115" s="14" t="s">
+      <c r="E117" s="14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="B116" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C116" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="E116" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
     </row>
     <row r="118">
       <c r="A118" s="15" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>35</v>
+        <v>282</v>
       </c>
       <c r="C118" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="E118" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="E118" s="14" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="B119" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C119" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>289</v>
-      </c>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
     </row>
     <row r="120">
       <c r="A120" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>35</v>
@@ -3799,15 +3673,15 @@
         <v>4</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>35</v>
@@ -3816,15 +3690,15 @@
         <v>4</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>226</v>
+        <v>288</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -3833,7 +3707,7 @@
     </row>
     <row r="123">
       <c r="A123" s="15" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>35</v>
@@ -3842,52 +3716,52 @@
         <v>4</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>226</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>35</v>
+        <v>296</v>
       </c>
       <c r="C124" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="C125" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D125" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E125" s="14" t="s">
         <v>302</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B126" s="11" t="s">
         <v>304</v>
-      </c>
-      <c r="B126" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="C126" s="16" t="s">
         <v>4</v>
@@ -3896,255 +3770,58 @@
         <v>305</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>234</v>
+        <v>306</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>35</v>
+        <v>304</v>
       </c>
       <c r="C127" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C128" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="15" t="s">
+      <c r="A129" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="B130" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C130" s="16" t="s">
+      <c r="B129" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C129" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D129" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="E130" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="15" t="s">
+      <c r="E129" s="14" t="s">
         <v>315</v>
-      </c>
-      <c r="B131" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="C131" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="E131" s="14" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="B133" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C133" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="B134" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C134" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D134" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="E134" s="14" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="B136" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B137" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="C137" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="E137" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="C138" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="E138" s="14" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="B139" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="C140" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="E140" s="14" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="B141" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C141" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="E141" s="14" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C142" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D142" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="E142" s="14" t="s">
-        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -4154,26 +3831,30 @@
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A132:E132"/>
-    <mergeCell ref="A135:E135"/>
   </mergeCells>
-  <dataValidations count="18">
+  <dataValidations count="14">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B27:B27">
+      <formula1>0</formula1>
+      <formula2>4</formula2>
+    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B28:B28">
       <formula1>0</formula1>
       <formula2>4</formula2>
@@ -4186,63 +3867,43 @@
       <formula1>0</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B31:B31">
-      <formula1>0</formula1>
-      <formula2>4</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B38:B38">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B37:B37">
       <formula1>0.001</formula1>
       <formula2>0.5</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B39:B39">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B38:B38">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B40:B40">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39:B39">
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B57:B57">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B56:B56">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B68:B68">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B64:B64">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B69:B69">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B65:B65">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B70:B70">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B66:B66">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B71:B71">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B67:B67">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B72:B72">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B68:B68">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B73:B73">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B74:B74">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B75:B75">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B76:B76">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B77:B77">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B69:B69">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -4251,7 +3912,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="49">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="45">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx"</xm:f>
@@ -4320,15 +3981,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>".,,"</xm:f>
           </x14:formula1>
-          <xm:sqref>B25:B25</xm:sqref>
+          <xm:sqref>B26:B26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>".,,"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B27:B27</xm:sqref>
+          <xm:sqref>B32:B32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4346,15 +4007,15 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B35:B35</xm:sqref>
+          <xm:sqref>B36:B36</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B37:B37</xm:sqref>
+          <xm:sqref>B40:B40</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
@@ -4368,15 +4029,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"primary,secondary"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B44:B44</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B43:B43</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"primary,secondary"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B45:B45</xm:sqref>
+          <xm:sqref>B46:B46</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4398,15 +4059,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"IQR"</xm:f>
           </x14:formula1>
           <xm:sqref>B50:B50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"IQR"</xm:f>
+            <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B51:B51</xm:sqref>
+          <xm:sqref>B52:B52</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4426,43 +4087,31 @@
           </x14:formula1>
           <xm:sqref>B55:B55</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B58:B58</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B56:B56</xm:sqref>
+          <xm:sqref>B60:B60</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"warm,cool,research,teal,red,brand"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B75:B75</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B59:B59</xm:sqref>
+          <xm:sqref>B91:B91</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B61:B61</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B63:B63</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"desc,asc,alphabetic"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B66:B66</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"warm,cool,research,teal,red,brand"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B83:B83</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
@@ -4470,25 +4119,19 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
           </x14:formula1>
-          <xm:sqref>B100:B100</xm:sqref>
+          <xm:sqref>B94:B94</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B101:B101</xm:sqref>
+          <xm:sqref>B97:B97</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B103:B103</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
           <xm:sqref>B106:B106</xm:sqref>
         </x14:dataValidation>
@@ -4496,55 +4139,49 @@
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
+          <xm:sqref>B107:B107</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
           <xm:sqref>B115:B115</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B116:B116</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B128:B128</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"FALSE,TRUE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B130:B130</xm:sqref>
+          <xm:sqref>B117:B117</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
           </x14:formula1>
-          <xm:sqref>B131:B131</xm:sqref>
+          <xm:sqref>B118:B118</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B137:B137</xm:sqref>
+          <xm:sqref>B124:B124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B138:B138</xm:sqref>
+          <xm:sqref>B125:B125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B139:B139</xm:sqref>
+          <xm:sqref>B126:B126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B140:B140</xm:sqref>
+          <xm:sqref>B127:B127</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4578,141 +4215,141 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>355</v>
+        <v>321</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>359</v>
+        <v>325</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>364</v>
+        <v>330</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>371</v>
+        <v>337</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>35</v>
@@ -4742,18 +4379,18 @@
         <v>35</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>35</v>
@@ -4765,7 +4402,7 @@
         <v>35</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>35</v>
@@ -4795,18 +4432,18 @@
         <v>35</v>
       </c>
       <c r="Q6" s="17" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>35</v>
@@ -4818,7 +4455,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>35</v>
@@ -4836,10 +4473,10 @@
         <v>35</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="O7" s="17" t="s">
         <v>35</v>
@@ -4848,18 +4485,18 @@
         <v>35</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>35</v>
@@ -4871,7 +4508,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>35</v>
@@ -4889,19 +4526,19 @@
         <v>35</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5916,122 +5553,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>409</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>412</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>417</v>
+        <v>383</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>430</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -6057,48 +5694,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>435</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>437</v>
+        <v>403</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>35</v>
@@ -6109,10 +5746,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>443</v>
+        <v>409</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>35</v>
@@ -6123,16 +5760,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>445</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8">
@@ -6337,42 +5974,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>447</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>448</v>
+        <v>414</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>453</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>455</v>
+        <v>421</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6380,10 +6017,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>456</v>
+        <v>422</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6517,56 +6154,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>458</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>459</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>465</v>
+        <v>431</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>467</v>
+        <v>433</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="455">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -247,6 +247,15 @@
     <t xml:space="preserve">Number of decimal places for Numeric question statistics (mean, median).</t>
   </si>
   <si>
+    <t xml:space="preserve">decimal_places</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General fallback: the workbook builder uses this for cells with no type-specific setting above. Blank = each consumer keeps its own default, which is what every report did before this row existed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 to 4, or leave blank</t>
+  </si>
+  <si>
     <t xml:space="preserve">BOX CATEGORY DISPLAY</t>
   </si>
   <si>
@@ -727,6 +736,12 @@
     <t xml:space="preserve">Add a Tracking tab to the v2 report, built from anonymised per-wave microdata. Requires html_report_v2=TRUE and a waves_source with prior waves' contributions. The standalone tracker module is unaffected.</t>
   </si>
   <si>
+    <t xml:space="preserve">html_report_v2_cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open SAVED copies of the v2 report on a cover page: report title, the Comments sheet's executive summary and background, and the first five Story pins as leading findings. Only affects copies made with Save copy, and only when there is story content to show. FALSE (the default) = saved copies open on the dashboard, as before.</t>
+  </si>
+  <si>
     <t xml:space="preserve">waves_source</t>
   </si>
   <si>
@@ -754,6 +769,39 @@
     <t xml:space="preserve">File path, or leave blank to auto-detect</t>
   </si>
   <si>
+    <t xml:space="preserve">TAB VISIBILITY (V2 REPORT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the Dashboard tab in the v2 report. FALSE withholds it from this build; the Crosstabs tab is always on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the Group overview (Patterns) tab in the v2 report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the Differences tab in the v2 report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the Tracking tab in the v2 report. It also needs html_report_v2_tracking = TRUE and at least one prior wave in waves_source — without those the tab is absent whatever this is set to.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">show_qualitative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the Qualitative (comment) tab in the v2 report. It also needs a qual_workbook that joins to the survey.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GROUP OVERVIEW TAB (OPTIONAL)</t>
   </si>
   <si>
@@ -799,9 +847,6 @@
     <t xml:space="preserve">Draft the Reader narrative with an AI model instead of the built-in template (only used when generate_reader_report = TRUE). Requires an Anthropic API key in the ANTHROPIC_API_KEY environment variable. Only aggregate figures are sent — never microdata or verbatims — and every number the model writes is checked against the data. If the model is unavailable the report falls back to the on-device narrative and says so.</t>
   </si>
   <si>
-    <t xml:space="preserve">ROW DESCRIPTORS (HTML Report)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ANALYST &amp; CLOSING SECTION</t>
   </si>
   <si>
@@ -1003,6 +1048,12 @@
     <t xml:space="preserve">KeyShare</t>
   </si>
   <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula</t>
+  </si>
+  <si>
     <t xml:space="preserve">BaseFilter</t>
   </si>
   <si>
@@ -1054,6 +1105,12 @@
     <t xml:space="preserve">[Optional] Single/Multi questions only: the exact option, box or NET label whose share summarises this question for the Group overview tab - where a HIGHER share is BETTER (e.g. 'Always' on delivery day, 'Not a problem' on language). Blank = question stays out of the Group overview scan. Ignored on rated questions (their index is used).</t>
   </si>
   <si>
+    <t xml:space="preserve">[Optional] Where this question's numbers come from - the survey question behind it, or the columns a derived figure was built from. Shown on the question card in the v2 report. Blank = the report says nothing about provenance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Derived questions only: how the figure was worked out, in plain words (e.g. 'monthly spend / monthly transactions, among buyers'). A question with a formula reads as DERIVED in the report; one with a Source and no formula reads as ASKED. Fill this in for any column computed before the data reached Turas - the engine sees only the finished column.</t>
+  </si>
+  <si>
     <t xml:space="preserve">[Optional] R expression to filter respondents (e.g. Q1 == "Male" or !is.na(Q20)). Leave blank for no filter.</t>
   </si>
   <si>
@@ -1213,7 +1270,7 @@
     <t xml:space="preserve">Question Comments &amp; Report Text</t>
   </si>
   <si>
-    <t xml:space="preserve">Add question-specific comments and report narrative sections. Use _BACKGROUND and _EXECUTIVE_SUMMARY for report sections.</t>
+    <t xml:space="preserve">Add question-specific comments and report narrative sections. Use _BACKGROUND, _EXECUTIVE_SUMMARY and _REPORT_CONSTRUCTION for report sections.</t>
   </si>
   <si>
     <t xml:space="preserve">Comment</t>
@@ -1225,7 +1282,7 @@
     <t xml:space="preserve">Headline</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Question code to attach comment to, or _BACKGROUND / _EXECUTIVE_SUMMARY for report sections.</t>
+    <t xml:space="preserve">[REQUIRED] Question code to attach comment to, or _BACKGROUND / _EXECUTIVE_SUMMARY / _REPORT_CONSTRUCTION for report sections.</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Comment text. Supports markdown for HTML reports (bold, bullets, links).</t>
@@ -1247,6 +1304,12 @@
   </si>
   <si>
     <t xml:space="preserve">Key finding: Overall satisfaction increased by 5 points year-on-year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_REPORT_CONSTRUCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional: how this study's numbers were built, when other stages sit around Turas. Replaces the WHOLE Report construction section in About, including the standard reproducibility, AI and author-review paragraphs. Blank leaves it unchanged.</t>
   </si>
   <si>
     <t xml:space="preserve">Note: Question wording changed from previous wave.</t>
@@ -2278,43 +2341,43 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="B31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="A32" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>33</v>
@@ -2322,62 +2385,62 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="A35" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="A36" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>0.05</v>
+        <v>87</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -2385,7 +2448,7 @@
         <v>89</v>
       </c>
       <c r="B38" s="11" t="n">
-        <v>30</v>
+        <v>0.05</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>15</v>
@@ -2398,14 +2461,14 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="10" t="s">
         <v>92</v>
       </c>
       <c r="B39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>93</v>
@@ -2415,34 +2478,34 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>15</v>
+      <c r="B40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>96</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="s">
-        <v>97</v>
+      <c r="A41" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>4</v>
+        <v>39</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>33</v>
@@ -2450,7 +2513,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>31</v>
@@ -2459,7 +2522,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>33</v>
@@ -2467,19 +2530,19 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -2487,47 +2550,47 @@
         <v>104</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E44" s="14" t="s">
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="s">
+      <c r="B45" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
+      <c r="C45" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="A46" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>31</v>
@@ -2536,7 +2599,7 @@
         <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>33</v>
@@ -2544,16 +2607,16 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>33</v>
@@ -2561,16 +2624,16 @@
     </row>
     <row r="49">
       <c r="A49" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>33</v>
@@ -2578,10 +2641,10 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>15</v>
@@ -2590,41 +2653,41 @@
         <v>119</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
+      <c r="B51" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="13" t="s">
+      <c r="A52" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E52" s="14" t="s">
-        <v>124</v>
-      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>15</v>
@@ -2633,163 +2696,163 @@
         <v>126</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
+      <c r="B57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B58" s="11" t="s">
+      <c r="A58" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E58" s="14" t="s">
+      <c r="D59" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E59" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-    </row>
     <row r="60">
-      <c r="A60" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B60" s="11" t="s">
+      <c r="A60" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C61" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E60" s="14" t="s">
+      <c r="D61" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-    </row>
     <row r="62">
-      <c r="A62" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" s="16" t="s">
+      <c r="A62" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
+      <c r="D63" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E64" s="14" t="s">
+      <c r="A64" s="9" t="s">
         <v>147</v>
       </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="s">
@@ -2805,24 +2868,24 @@
         <v>149</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B66" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67">
@@ -2830,7 +2893,7 @@
         <v>153</v>
       </c>
       <c r="B67" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>15</v>
@@ -2839,95 +2902,95 @@
         <v>154</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B68" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B69" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
+      <c r="A70" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" s="13" t="s">
+      <c r="A71" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E71" s="14" t="s">
-        <v>163</v>
-      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>164</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>165</v>
       </c>
       <c r="C72" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E72" s="14" t="s">
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="15" t="s">
+      <c r="B73" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B73" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" s="16" t="s">
-        <v>4</v>
+      <c r="C73" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>169</v>
@@ -2937,28 +3000,28 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="15" t="s">
         <v>171</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>172</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C75" s="12" t="s">
         <v>15</v>
@@ -2967,18 +3030,18 @@
         <v>175</v>
       </c>
       <c r="E75" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="15" t="s">
+      <c r="B76" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B76" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>4</v>
+      <c r="C76" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>178</v>
@@ -3124,42 +3187,42 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="15" t="s">
         <v>204</v>
       </c>
       <c r="B85" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="E85" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C86" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D86" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E86" s="14" t="s">
         <v>206</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>35</v>
@@ -3168,10 +3231,10 @@
         <v>4</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88">
@@ -3188,12 +3251,12 @@
         <v>213</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>35</v>
@@ -3202,50 +3265,50 @@
         <v>4</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
+      <c r="B90" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="A91" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
     </row>
     <row r="92">
       <c r="A92" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C92" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E92" s="14" t="s">
         <v>33</v>
@@ -3253,19 +3316,19 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C93" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>224</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
@@ -3273,24 +3336,24 @@
         <v>225</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>226</v>
+        <v>35</v>
       </c>
       <c r="C94" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D94" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="E94" s="14" t="s">
         <v>227</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B95" s="11" t="s">
         <v>229</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="C95" s="16" t="s">
         <v>4</v>
@@ -3316,41 +3379,41 @@
         <v>233</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C97" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C98" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>238</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99">
@@ -3358,7 +3421,7 @@
         <v>239</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C99" s="16" t="s">
         <v>4</v>
@@ -3367,12 +3430,12 @@
         <v>240</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>35</v>
@@ -3381,24 +3444,32 @@
         <v>4</v>
       </c>
       <c r="D100" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E100" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="E100" s="14" t="s">
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="s">
+      <c r="B101" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="B101" s="9"/>
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
+      <c r="E101" s="14" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>35</v>
@@ -3407,67 +3478,67 @@
         <v>4</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C103" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D103" s="13" t="s">
+      <c r="A103" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E103" s="14" t="s">
-        <v>251</v>
-      </c>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
     </row>
     <row r="104">
       <c r="A104" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C104" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D104" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="E104" s="14" t="s">
+      <c r="B105" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" s="13" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
+      <c r="E105" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C106" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>33</v>
@@ -3475,29 +3546,37 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C107" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="s">
+      <c r="A108" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="9"/>
+      <c r="E108" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="s">
@@ -3522,12 +3601,12 @@
         <v>263</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>35</v>
@@ -3536,15 +3615,15 @@
         <v>4</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>35</v>
@@ -3553,35 +3632,27 @@
         <v>4</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C113" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D113" s="13" t="s">
+      <c r="A113" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="E113" s="14" t="s">
-        <v>211</v>
-      </c>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
     </row>
     <row r="114">
       <c r="A114" s="15" t="s">
         <v>272</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C114" s="16" t="s">
         <v>4</v>
@@ -3590,29 +3661,29 @@
         <v>273</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>274</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="C115" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>277</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
@@ -3621,50 +3692,58 @@
     </row>
     <row r="117">
       <c r="A117" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C117" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>33</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>282</v>
+        <v>35</v>
       </c>
       <c r="C118" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="E118" s="14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="E118" s="14" t="s">
+      <c r="E119" s="14" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
     </row>
     <row r="120">
       <c r="A120" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>35</v>
@@ -3673,15 +3752,15 @@
         <v>4</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>35</v>
@@ -3690,109 +3769,101 @@
         <v>4</v>
       </c>
       <c r="D121" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="E121" s="14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="E121" s="14" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="s">
+      <c r="B122" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
+      <c r="E122" s="14" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="B123" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C123" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D123" s="13" t="s">
+      <c r="A123" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="E123" s="14" t="s">
-        <v>294</v>
-      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>296</v>
+        <v>31</v>
       </c>
       <c r="C124" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>298</v>
+        <v>33</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C125" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="B126" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="C126" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>306</v>
-      </c>
+      <c r="A126" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="9"/>
     </row>
     <row r="127">
       <c r="A127" s="15" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>304</v>
+        <v>35</v>
       </c>
       <c r="C127" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="15" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>35</v>
@@ -3801,27 +3872,138 @@
         <v>4</v>
       </c>
       <c r="D128" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E128" s="14" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B131" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="E128" s="14" t="s">
+      <c r="C131" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D131" s="13" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="15" t="s">
+      <c r="E131" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="B129" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C129" s="16" t="s">
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="C132" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="E129" s="14" t="s">
-        <v>315</v>
+      <c r="D132" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D133" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="E133" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D134" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E134" s="14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E135" s="14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="E136" s="14" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -3832,25 +4014,25 @@
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A103:E103"/>
     <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A119:E119"/>
-    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A129:E129"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="15">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B27:B27">
       <formula1>0</formula1>
       <formula2>4</formula2>
@@ -3867,32 +4049,32 @@
       <formula1>0</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B37:B37">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B31:B31">
+      <formula1>0</formula1>
+      <formula2>4</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B38:B38">
       <formula1>0.001</formula1>
       <formula2>0.5</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B38:B38">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B39:B39">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B39:B39">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B40:B40">
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B56:B56">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B57:B57">
       <formula1>0</formula1>
       <formula2>3</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B64:B64">
-      <formula1>1</formula1>
-      <formula2>100</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B65:B65">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B66:B66">
-      <formula1>0</formula1>
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B66:B66">
+      <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B67:B67">
@@ -3907,12 +4089,16 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B70:B70">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="45">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="51">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx"</xm:f>
@@ -3989,12 +4175,6 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B32:B32</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
           <xm:sqref>B33:B33</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
@@ -4007,15 +4187,15 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B36:B36</xm:sqref>
+          <xm:sqref>B35:B35</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B40:B40</xm:sqref>
+          <xm:sqref>B37:B37</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
@@ -4029,15 +4209,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B43:B43</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"primary,secondary"</xm:f>
           </x14:formula1>
-          <xm:sqref>B44:B44</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B46:B46</xm:sqref>
+          <xm:sqref>B45:B45</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4059,15 +4239,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"IQR"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
           <xm:sqref>B50:B50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
+            <xm:f>"IQR"</xm:f>
           </x14:formula1>
-          <xm:sqref>B52:B52</xm:sqref>
+          <xm:sqref>B51:B51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4087,29 +4267,29 @@
           </x14:formula1>
           <xm:sqref>B55:B55</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B56:B56</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B58:B58</xm:sqref>
+          <xm:sqref>B59:B59</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B60:B60</xm:sqref>
+          <xm:sqref>B61:B61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"warm,cool,research,teal,red,brand"</xm:f>
           </x14:formula1>
-          <xm:sqref>B75:B75</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B91:B91</xm:sqref>
+          <xm:sqref>B76:B76</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4119,69 +4299,111 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B93:B93</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
             <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
           </x14:formula1>
-          <xm:sqref>B94:B94</xm:sqref>
+          <xm:sqref>B95:B95</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B97:B97</xm:sqref>
+          <xm:sqref>B98:B98</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B99:B99</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B104:B104</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B105:B105</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B106:B106</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B107:B107</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B108:B108</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B106:B106</xm:sqref>
+          <xm:sqref>B114:B114</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B107:B107</xm:sqref>
+          <xm:sqref>B115:B115</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B115:B115</xm:sqref>
+          <xm:sqref>B122:B122</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B117:B117</xm:sqref>
+          <xm:sqref>B124:B124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
           </x14:formula1>
-          <xm:sqref>B118:B118</xm:sqref>
+          <xm:sqref>B125:B125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B124:B124</xm:sqref>
+          <xm:sqref>B131:B131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B125:B125</xm:sqref>
+          <xm:sqref>B132:B132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B126:B126</xm:sqref>
+          <xm:sqref>B133:B133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B127:B127</xm:sqref>
+          <xm:sqref>B134:B134</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4204,152 +4426,166 @@
     <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="35.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="30.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="22.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="30.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="40.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="35.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="30.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="22.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="16.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="40.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="14.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="16.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>334</v>
+        <v>349</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>351</v>
+        <v>368</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>35</v>
@@ -4379,18 +4615,24 @@
         <v>35</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>355</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" s="17" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>35</v>
@@ -4402,7 +4644,7 @@
         <v>35</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>35</v>
@@ -4432,18 +4674,24 @@
         <v>35</v>
       </c>
       <c r="Q6" s="17" t="s">
-        <v>357</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>35</v>
@@ -4455,7 +4703,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>35</v>
@@ -4473,30 +4721,36 @@
         <v>35</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>359</v>
+        <v>35</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>356</v>
+        <v>35</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>35</v>
+        <v>378</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>360</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>35</v>
@@ -4508,7 +4762,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>35</v>
@@ -4526,19 +4780,25 @@
         <v>35</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>361</v>
+        <v>35</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>364</v>
+        <v>382</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -4559,6 +4819,8 @@
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -4578,6 +4840,8 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -4597,6 +4861,8 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -4616,6 +4882,8 @@
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -4635,6 +4903,8 @@
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -4654,6 +4924,8 @@
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -4673,6 +4945,8 @@
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -4692,6 +4966,8 @@
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -4711,6 +4987,8 @@
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -4730,6 +5008,8 @@
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -4749,6 +5029,8 @@
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -4768,6 +5050,8 @@
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
@@ -4787,6 +5071,8 @@
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
@@ -4806,6 +5092,8 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
@@ -4825,6 +5113,8 @@
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
@@ -4844,6 +5134,8 @@
       <c r="O24" s="11"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
@@ -4863,6 +5155,8 @@
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
@@ -4882,6 +5176,8 @@
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
@@ -4901,6 +5197,8 @@
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
     </row>
     <row r="28">
       <c r="A28" s="11"/>
@@ -4920,6 +5218,8 @@
       <c r="O28" s="11"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
     </row>
     <row r="29">
       <c r="A29" s="11"/>
@@ -4939,6 +5239,8 @@
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
@@ -4958,6 +5260,8 @@
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
     </row>
     <row r="31">
       <c r="A31" s="11"/>
@@ -4977,6 +5281,8 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
     </row>
     <row r="32">
       <c r="A32" s="11"/>
@@ -4996,6 +5302,8 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
     </row>
     <row r="33">
       <c r="A33" s="11"/>
@@ -5015,6 +5323,8 @@
       <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
     </row>
     <row r="34">
       <c r="A34" s="11"/>
@@ -5034,6 +5344,8 @@
       <c r="O34" s="11"/>
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
     </row>
     <row r="35">
       <c r="A35" s="11"/>
@@ -5053,6 +5365,8 @@
       <c r="O35" s="11"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
     </row>
     <row r="36">
       <c r="A36" s="11"/>
@@ -5072,6 +5386,8 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
     </row>
     <row r="37">
       <c r="A37" s="11"/>
@@ -5091,6 +5407,8 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
     </row>
     <row r="38">
       <c r="A38" s="11"/>
@@ -5110,6 +5428,8 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
     </row>
     <row r="39">
       <c r="A39" s="11"/>
@@ -5129,6 +5449,8 @@
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
     </row>
     <row r="40">
       <c r="A40" s="11"/>
@@ -5148,6 +5470,8 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
     </row>
     <row r="41">
       <c r="A41" s="11"/>
@@ -5167,6 +5491,8 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
     </row>
     <row r="42">
       <c r="A42" s="11"/>
@@ -5186,6 +5512,8 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
     </row>
     <row r="43">
       <c r="A43" s="11"/>
@@ -5205,6 +5533,8 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
     </row>
     <row r="44">
       <c r="A44" s="11"/>
@@ -5224,6 +5554,8 @@
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
     </row>
     <row r="45">
       <c r="A45" s="11"/>
@@ -5243,6 +5575,8 @@
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
     </row>
     <row r="46">
       <c r="A46" s="11"/>
@@ -5262,6 +5596,8 @@
       <c r="O46" s="11"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
     </row>
     <row r="47">
       <c r="A47" s="11"/>
@@ -5281,6 +5617,8 @@
       <c r="O47" s="11"/>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
     </row>
     <row r="48">
       <c r="A48" s="11"/>
@@ -5300,6 +5638,8 @@
       <c r="O48" s="11"/>
       <c r="P48" s="11"/>
       <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
     </row>
     <row r="49">
       <c r="A49" s="11"/>
@@ -5319,6 +5659,8 @@
       <c r="O49" s="11"/>
       <c r="P49" s="11"/>
       <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
     </row>
     <row r="50">
       <c r="A50" s="11"/>
@@ -5338,6 +5680,8 @@
       <c r="O50" s="11"/>
       <c r="P50" s="11"/>
       <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
     </row>
     <row r="51">
       <c r="A51" s="11"/>
@@ -5357,6 +5701,8 @@
       <c r="O51" s="11"/>
       <c r="P51" s="11"/>
       <c r="Q51" s="11"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="11"/>
     </row>
     <row r="52">
       <c r="A52" s="11"/>
@@ -5376,6 +5722,8 @@
       <c r="O52" s="11"/>
       <c r="P52" s="11"/>
       <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
     </row>
     <row r="53">
       <c r="A53" s="11"/>
@@ -5395,6 +5743,8 @@
       <c r="O53" s="11"/>
       <c r="P53" s="11"/>
       <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
     </row>
     <row r="54">
       <c r="A54" s="11"/>
@@ -5414,6 +5764,8 @@
       <c r="O54" s="11"/>
       <c r="P54" s="11"/>
       <c r="Q54" s="11"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
     </row>
     <row r="55">
       <c r="A55" s="11"/>
@@ -5433,6 +5785,8 @@
       <c r="O55" s="11"/>
       <c r="P55" s="11"/>
       <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
     </row>
     <row r="56">
       <c r="A56" s="11"/>
@@ -5452,6 +5806,8 @@
       <c r="O56" s="11"/>
       <c r="P56" s="11"/>
       <c r="Q56" s="11"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
     </row>
     <row r="57">
       <c r="A57" s="11"/>
@@ -5471,6 +5827,8 @@
       <c r="O57" s="11"/>
       <c r="P57" s="11"/>
       <c r="Q57" s="11"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="11"/>
     </row>
     <row r="58">
       <c r="A58" s="11"/>
@@ -5490,11 +5848,13 @@
       <c r="O58" s="11"/>
       <c r="P58" s="11"/>
       <c r="Q58" s="11"/>
+      <c r="R58" s="11"/>
+      <c r="S58" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F58">
@@ -5553,122 +5913,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5694,48 +6054,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>35</v>
@@ -5746,10 +6106,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>35</v>
@@ -5760,23 +6120,31 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>356</v>
+        <v>429</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>411</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
+      <c r="A8" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -5951,6 +6319,12 @@
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5974,42 +6348,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6017,10 +6391,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6154,56 +6528,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -10,14 +10,15 @@
     <sheet name="Selection" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Base Filters Reference" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Comments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="AddedSlides" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Population" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ReportText" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AddedSlides" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Population" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -61,7 +62,7 @@
     <t xml:space="preserve">structure_file</t>
   </si>
   <si>
-    <t xml:space="preserve">Survey_Structure.xlsx</t>
+    <t xml:space="preserve">Survey_Structure_Template.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">REQUIRED</t>
@@ -367,6 +368,12 @@
     <t xml:space="preserve">Show mode (most frequent value) for Numeric-type questions (unweighted only).</t>
   </si>
   <si>
+    <t xml:space="preserve">show_numeric_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show the Standard Deviation row on Numeric-type questions. Turn off for skewed measures (spend, counts) where the SD exceeds the mean and says less than the bins above it.</t>
+  </si>
+  <si>
     <t xml:space="preserve">show_numeric_outliers</t>
   </si>
   <si>
@@ -742,6 +749,15 @@
     <t xml:space="preserve">Open SAVED copies of the v2 report on a cover page: report title, the Comments sheet's executive summary and background, and the first five Story pins as leading findings. Only affects copies made with Save copy, and only when there is story content to show. FALSE (the default) = saved copies open on the dashboard, as before.</t>
   </si>
   <si>
+    <t xml:space="preserve">html_report_v2_cover_findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many Story pins the cover lists as leading findings. Blank = 5. ALL = every pin, however many. When the cover does stop short it says so on the page ("Showing 5 of 12 pinned findings"). Note the exported PowerPoint cover is a single slide and always shows the first 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole number of 1 or more, ALL, or leave blank for 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">waves_source</t>
   </si>
   <si>
@@ -832,6 +848,15 @@
     <t xml:space="preserve">Comma-separated question codes, or leave blank</t>
   </si>
   <si>
+    <t xml:space="preserve">insight_exclude_categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category names (from the Selection sheet's Category column) whose questions the Differences tab and the Group overview KeyShare scan treat as cuts, not outcomes - e.g. imputed or modelled measures a study does not want leading its findings. Case-insensitive; adds to the built-in demographics/corpographics detection. The questions stay in the crosstabs. Blank = built-in detection only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated category names, or leave blank</t>
+  </si>
+  <si>
     <t xml:space="preserve">READER REPORT (OPTIONAL)</t>
   </si>
   <si>
@@ -1316,6 +1341,24 @@
   </si>
   <si>
     <t xml:space="preserve">Satisfaction is up 5 points, driven by service quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report Text Overrides (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leave empty unless this study must word something differently from every other study. Platform wording is edited once, in the Callout Editor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Text key to override for THIS study only, e.g. cards.sig.letters. Find the key by opening a report and pressing ctrl+alt+K, or in the Callout Editor under module 'tabs'. An unknown key stops the report build rather than being ignored.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Replacement wording for this study. Leave blank to use the platform text. Same rules as the editor: inline markup only (strong, em, li, sup...), balanced, no attributes; keep any {placeholders} the key declares.</t>
   </si>
   <si>
     <t xml:space="preserve">Additional Report Slides</t>
@@ -2623,14 +2666,14 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="15" t="s">
         <v>116</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>15</v>
+      <c r="C49" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>117</v>
@@ -2644,7 +2687,7 @@
         <v>118</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>15</v>
@@ -2661,59 +2704,59 @@
         <v>120</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="s">
+      <c r="B52" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
+      <c r="C52" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B53" s="11" t="s">
+      <c r="A53" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>127</v>
-      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54" s="14" t="s">
         <v>129</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="55">
@@ -2721,7 +2764,7 @@
         <v>130</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>15</v>
@@ -2730,7 +2773,7 @@
         <v>131</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56">
@@ -2738,7 +2781,7 @@
         <v>132</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>15</v>
@@ -2747,15 +2790,15 @@
         <v>133</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="11" t="n">
-        <v>1</v>
+      <c r="B57" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>15</v>
@@ -2764,116 +2807,116 @@
         <v>135</v>
       </c>
       <c r="E57" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="s">
+      <c r="B58" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
+      <c r="E58" s="14" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B59" s="11" t="s">
+      <c r="A59" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C60" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E59" s="14" t="s">
+      <c r="D60" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-    </row>
     <row r="61">
-      <c r="A61" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B61" s="11" t="s">
+      <c r="A61" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C62" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" s="14" t="s">
+      <c r="D62" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E62" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-    </row>
     <row r="63">
-      <c r="A63" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C63" s="16" t="s">
+      <c r="A63" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="s">
+      <c r="D64" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
+      <c r="E64" s="14" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="13" t="s">
+      <c r="A65" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E65" s="14" t="s">
-        <v>150</v>
-      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B66" s="11" t="n">
         <v>10</v>
@@ -2882,10 +2925,10 @@
         <v>15</v>
       </c>
       <c r="D66" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" s="14" t="s">
         <v>152</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="67">
@@ -2893,7 +2936,7 @@
         <v>153</v>
       </c>
       <c r="B67" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>15</v>
@@ -2902,24 +2945,24 @@
         <v>154</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B68" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E68" s="14" t="s">
         <v>157</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="69">
@@ -2927,7 +2970,7 @@
         <v>158</v>
       </c>
       <c r="B69" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>15</v>
@@ -2936,7 +2979,7 @@
         <v>159</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70">
@@ -2944,7 +2987,7 @@
         <v>160</v>
       </c>
       <c r="B70" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>15</v>
@@ -2953,84 +2996,84 @@
         <v>161</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
+      <c r="B71" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B72" s="11" t="s">
+      <c r="A72" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>166</v>
-      </c>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D73" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="B74" s="11" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="15" t="s">
+      <c r="C74" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" s="16" t="s">
+      <c r="E74" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="s">
+      <c r="D75" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B75" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="13" t="s">
+      <c r="E75" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="E75" s="14" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="76">
@@ -3038,38 +3081,38 @@
         <v>176</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C76" s="12" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="B77" s="11" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="s">
+      <c r="C77" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B77" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D77" s="13" t="s">
+      <c r="E77" s="14" t="s">
         <v>181</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>35</v>
@@ -3078,15 +3121,15 @@
         <v>4</v>
       </c>
       <c r="D78" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E78" s="14" t="s">
         <v>184</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>35</v>
@@ -3095,15 +3138,15 @@
         <v>4</v>
       </c>
       <c r="D79" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" s="14" t="s">
         <v>187</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>35</v>
@@ -3112,15 +3155,15 @@
         <v>4</v>
       </c>
       <c r="D80" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E80" s="14" t="s">
         <v>190</v>
-      </c>
-      <c r="E80" s="14" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>35</v>
@@ -3129,15 +3172,15 @@
         <v>4</v>
       </c>
       <c r="D81" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E81" s="14" t="s">
         <v>193</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>35</v>
@@ -3146,15 +3189,15 @@
         <v>4</v>
       </c>
       <c r="D82" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E82" s="14" t="s">
         <v>196</v>
-      </c>
-      <c r="E82" s="14" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>35</v>
@@ -3163,15 +3206,15 @@
         <v>4</v>
       </c>
       <c r="D83" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E83" s="14" t="s">
         <v>199</v>
-      </c>
-      <c r="E83" s="14" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>35</v>
@@ -3180,15 +3223,15 @@
         <v>4</v>
       </c>
       <c r="D84" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E84" s="14" t="s">
         <v>202</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>35</v>
@@ -3197,44 +3240,44 @@
         <v>4</v>
       </c>
       <c r="D85" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E85" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="E85" s="14" t="s">
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="s">
+      <c r="B86" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="E86" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="C86" s="12" t="s">
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C87" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C87" s="16" t="s">
-        <v>4</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>211</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="88">
@@ -3251,12 +3294,12 @@
         <v>213</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>35</v>
@@ -3265,10 +3308,10 @@
         <v>4</v>
       </c>
       <c r="D89" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E89" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="90">
@@ -3285,41 +3328,41 @@
         <v>218</v>
       </c>
       <c r="E90" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="s">
+      <c r="B91" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
+      <c r="E91" s="14" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D92" s="13" t="s">
+      <c r="A92" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E92" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
     </row>
     <row r="93">
       <c r="A93" s="15" t="s">
         <v>223</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C93" s="16" t="s">
         <v>4</v>
@@ -3336,7 +3379,7 @@
         <v>225</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C94" s="16" t="s">
         <v>4</v>
@@ -3345,46 +3388,46 @@
         <v>226</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>227</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>229</v>
+        <v>35</v>
       </c>
       <c r="C95" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="C96" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D96" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="E96" s="14" t="s">
         <v>233</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>35</v>
@@ -3393,10 +3436,10 @@
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E97" s="14" t="s">
         <v>236</v>
-      </c>
-      <c r="E97" s="14" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="98">
@@ -3404,7 +3447,7 @@
         <v>237</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C98" s="16" t="s">
         <v>4</v>
@@ -3413,7 +3456,7 @@
         <v>238</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
     </row>
     <row r="99">
@@ -3438,7 +3481,7 @@
         <v>241</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C100" s="16" t="s">
         <v>4</v>
@@ -3447,12 +3490,12 @@
         <v>242</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>35</v>
@@ -3461,15 +3504,15 @@
         <v>4</v>
       </c>
       <c r="D101" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E101" s="14" t="s">
         <v>245</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>35</v>
@@ -3478,58 +3521,58 @@
         <v>4</v>
       </c>
       <c r="D102" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="E102" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="E102" s="14" t="s">
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="s">
+      <c r="B103" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D103" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
+      <c r="E103" s="14" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C104" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>33</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B105" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C105" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>33</v>
-      </c>
+      <c r="A105" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
     </row>
     <row r="106">
       <c r="A106" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>39</v>
@@ -3538,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>33</v>
@@ -3546,7 +3589,7 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>39</v>
@@ -3555,7 +3598,7 @@
         <v>4</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>33</v>
@@ -3563,7 +3606,7 @@
     </row>
     <row r="108">
       <c r="A108" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>39</v>
@@ -3572,58 +3615,58 @@
         <v>4</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="B109" s="9"/>
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
+      <c r="A109" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E109" s="14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C110" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>264</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C111" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D111" s="13" t="s">
+      <c r="A111" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E111" s="14" t="s">
-        <v>267</v>
-      </c>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
     </row>
     <row r="112">
       <c r="A112" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>35</v>
@@ -3632,58 +3675,66 @@
         <v>4</v>
       </c>
       <c r="D112" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E112" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="E112" s="14" t="s">
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="s">
+      <c r="B113" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D113" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="B113" s="9"/>
-      <c r="C113" s="9"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="9"/>
+      <c r="E113" s="14" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C114" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>33</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C115" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>33</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
@@ -3692,54 +3743,46 @@
     </row>
     <row r="117">
       <c r="A117" s="15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C117" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>206</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C118" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>281</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B119" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C119" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E119" s="14" t="s">
+      <c r="A119" s="9" t="s">
         <v>284</v>
       </c>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
     </row>
     <row r="120">
       <c r="A120" s="15" t="s">
@@ -3755,7 +3798,7 @@
         <v>286</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121">
@@ -3780,7 +3823,7 @@
         <v>290</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="C122" s="16" t="s">
         <v>4</v>
@@ -3793,51 +3836,59 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="s">
+      <c r="A123" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
+      <c r="B123" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E123" s="14" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C124" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>33</v>
+        <v>297</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>297</v>
+        <v>127</v>
       </c>
       <c r="C125" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -3846,19 +3897,19 @@
     </row>
     <row r="127">
       <c r="A127" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C127" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>303</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128">
@@ -3866,21 +3917,21 @@
         <v>304</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>35</v>
+        <v>305</v>
       </c>
       <c r="C128" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -3889,7 +3940,7 @@
     </row>
     <row r="130">
       <c r="A130" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>35</v>
@@ -3898,66 +3949,58 @@
         <v>4</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>311</v>
+        <v>35</v>
       </c>
       <c r="C131" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="15" t="s">
+      <c r="A132" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B132" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="C132" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D132" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>317</v>
-      </c>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
     </row>
     <row r="133">
       <c r="A133" s="15" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>319</v>
+        <v>35</v>
       </c>
       <c r="C133" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="15" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>319</v>
@@ -3966,44 +4009,95 @@
         <v>4</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>35</v>
+        <v>323</v>
       </c>
       <c r="C135" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E135" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>35</v>
+        <v>327</v>
       </c>
       <c r="C136" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D136" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="E136" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="E136" s="14" t="s">
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="s">
         <v>330</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E137" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E138" s="14" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E139" s="14" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4017,20 +4111,20 @@
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A111:E111"/>
     <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A126:E126"/>
     <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A132:E132"/>
   </mergeCells>
   <dataValidations count="15">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B27:B27">
@@ -4065,20 +4159,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B57:B57">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B58:B58">
       <formula1>0</formula1>
       <formula2>3</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B65:B65">
-      <formula1>1</formula1>
-      <formula2>100</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B66:B66">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B67:B67">
-      <formula1>0</formula1>
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B67:B67">
+      <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B68:B68">
@@ -4093,12 +4183,16 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B71:B71">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="51">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="52">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"xlsx"</xm:f>
@@ -4231,7 +4325,7 @@
           </x14:formula1>
           <xm:sqref>B48:B48</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
@@ -4245,15 +4339,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"IQR"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
           <xm:sqref>B51:B51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Y,N"</xm:f>
+            <xm:f>"IQR"</xm:f>
           </x14:formula1>
-          <xm:sqref>B53:B53</xm:sqref>
+          <xm:sqref>B52:B52</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4273,29 +4367,29 @@
           </x14:formula1>
           <xm:sqref>B56:B56</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B57:B57</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B59:B59</xm:sqref>
+          <xm:sqref>B60:B60</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B61:B61</xm:sqref>
+          <xm:sqref>B62:B62</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"warm,cool,research,teal,red,brand"</xm:f>
           </x14:formula1>
-          <xm:sqref>B76:B76</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B92:B92</xm:sqref>
+          <xm:sqref>B77:B77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4305,15 +4399,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B95:B95</xm:sqref>
+          <xm:sqref>B94:B94</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"Not_Specified,Random,Stratified,Cluster,Census,Quota,Online_Panel,Convenience"</xm:f>
           </x14:formula1>
-          <xm:sqref>B98:B98</xm:sqref>
+          <xm:sqref>B96:B96</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4325,13 +4419,7 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B104:B104</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B105:B105</xm:sqref>
+          <xm:sqref>B100:B100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -4353,57 +4441,69 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"FALSE,TRUE"</xm:f>
+            <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B114:B114</xm:sqref>
+          <xm:sqref>B109:B109</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B110:B110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B115:B115</xm:sqref>
+          <xm:sqref>B117:B117</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"FALSE,TRUE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B118:B118</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B122:B122</xm:sqref>
+          <xm:sqref>B125:B125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"FALSE,TRUE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B124:B124</xm:sqref>
+          <xm:sqref>B127:B127</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Sonnet 4.6,Opus 4.8"</xm:f>
           </x14:formula1>
-          <xm:sqref>B125:B125</xm:sqref>
+          <xm:sqref>B128:B128</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"hidden,redacted,full"</xm:f>
           </x14:formula1>
-          <xm:sqref>B131:B131</xm:sqref>
+          <xm:sqref>B134:B134</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"allow,safe,block"</xm:f>
           </x14:formula1>
-          <xm:sqref>B132:B132</xm:sqref>
+          <xm:sqref>B135:B135</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy,must_read,priority"</xm:f>
           </x14:formula1>
-          <xm:sqref>B133:B133</xm:sqref>
+          <xm:sqref>B136:B136</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"all,noteworthy"</xm:f>
           </x14:formula1>
-          <xm:sqref>B134:B134</xm:sqref>
+          <xm:sqref>B137:B137</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4439,153 +4539,153 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>35</v>
@@ -4621,18 +4721,18 @@
         <v>35</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>35</v>
@@ -4644,7 +4744,7 @@
         <v>35</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>35</v>
@@ -4680,18 +4780,18 @@
         <v>35</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>35</v>
@@ -4703,7 +4803,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>35</v>
@@ -4727,10 +4827,10 @@
         <v>35</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="Q7" s="17" t="s">
         <v>35</v>
@@ -4739,19 +4839,19 @@
         <v>35</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>372</v>
-      </c>
       <c r="D8" s="17" t="s">
         <v>35</v>
       </c>
@@ -4762,7 +4862,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>35</v>
@@ -4786,19 +4886,19 @@
         <v>35</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -5913,122 +6013,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -6054,48 +6154,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>35</v>
@@ -6106,10 +6206,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>35</v>
@@ -6120,10 +6220,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>35</v>
@@ -6134,16 +6234,16 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -6341,6 +6441,131 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
+    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="90.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
     <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="70.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
@@ -6348,42 +6573,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6391,10 +6616,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6516,7 +6741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -6528,56 +6753,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7">

--- a/modules/tabs/templates/Crosstab_Config_Template.xlsx
+++ b/modules/tabs/templates/Crosstab_Config_Template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="471">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">structure_file</t>
   </si>
   <si>
-    <t xml:space="preserve">Survey_Structure_Template.xlsx</t>
+    <t xml:space="preserve">Survey_Structure.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">REQUIRED</t>
@@ -1073,6 +1073,9 @@
     <t xml:space="preserve">KeyShare</t>
   </si>
   <si>
+    <t xml:space="preserve">ExcludeFromInsights</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source</t>
   </si>
   <si>
@@ -1128,6 +1131,9 @@
   </si>
   <si>
     <t xml:space="preserve">[Optional] Single/Multi questions only: the exact option, box or NET label whose share summarises this question for the Group overview tab - where a HIGHER share is BETTER (e.g. 'Always' on delivery day, 'Not a problem' on language). Blank = question stays out of the Group overview scan. Ignored on rated questions (their index is used).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Y = keep this question OUT of the Differences tab's findings, while it stays in the crosstabs as normal. Use it when several near-duplicate views of one measure (Own / Other / Total) each raise their own card, or when a modelled figure should not lead a lay reader's page. Blank = the question can raise findings. The Group overview scan ignores this column by design - it is a Differences-tab lever only.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] Where this question's numbers come from - the survey question behind it, or the columns a derived figure was built from. Shown on the question card in the v2 report. Blank = the report says nothing about provenance.</t>
@@ -4526,15 +4532,16 @@
     <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="30.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="40.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="35.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="30.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="22.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="16.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="14.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="16.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="40.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="30.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="40.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="35.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="30.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="22.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="14.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4605,87 +4612,93 @@
       <c r="S3" s="8" t="s">
         <v>359</v>
       </c>
+      <c r="T3" s="8" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>127</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>35</v>
@@ -4721,18 +4734,21 @@
         <v>35</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>382</v>
+        <v>35</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>127</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>35</v>
@@ -4780,77 +4796,83 @@
         <v>35</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>384</v>
+        <v>35</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="P7" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>35</v>
-      </c>
       <c r="R7" s="17" t="s">
         <v>35</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>387</v>
+        <v>35</v>
+      </c>
+      <c r="T7" s="17" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>127</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>35</v>
@@ -4862,7 +4884,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>35</v>
@@ -4886,19 +4908,22 @@
         <v>35</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>389</v>
+        <v>35</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q8" s="17" t="s">
         <v>390</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
+      </c>
+      <c r="T8" s="17" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -4921,6 +4946,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -4942,6 +4968,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -4963,6 +4990,7 @@
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -4984,6 +5012,7 @@
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -5005,6 +5034,7 @@
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -5026,6 +5056,7 @@
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -5047,6 +5078,7 @@
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -5068,6 +5100,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -5089,6 +5122,7 @@
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -5110,6 +5144,7 @@
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -5131,6 +5166,7 @@
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -5152,6 +5188,7 @@
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
@@ -5173,6 +5210,7 @@
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
@@ -5194,6 +5232,7 @@
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
@@ -5215,6 +5254,7 @@
       <c r="Q23" s="11"/>
       <c r="R23" s="11"/>
       <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
@@ -5236,6 +5276,7 @@
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
@@ -5257,6 +5298,7 @@
       <c r="Q25" s="11"/>
       <c r="R25" s="11"/>
       <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
@@ -5278,6 +5320,7 @@
       <c r="Q26" s="11"/>
       <c r="R26" s="11"/>
       <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
@@ -5299,6 +5342,7 @@
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
       <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
     </row>
     <row r="28">
       <c r="A28" s="11"/>
@@ -5320,6 +5364,7 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
       <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
     </row>
     <row r="29">
       <c r="A29" s="11"/>
@@ -5341,6 +5386,7 @@
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
       <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
@@ -5362,6 +5408,7 @@
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
     </row>
     <row r="31">
       <c r="A31" s="11"/>
@@ -5383,6 +5430,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
       <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
     </row>
     <row r="32">
       <c r="A32" s="11"/>
@@ -5404,6 +5452,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
       <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
     </row>
     <row r="33">
       <c r="A33" s="11"/>
@@ -5425,6 +5474,7 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
       <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
     </row>
     <row r="34">
       <c r="A34" s="11"/>
@@ -5446,6 +5496,7 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
       <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
     </row>
     <row r="35">
       <c r="A35" s="11"/>
@@ -5467,6 +5518,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
       <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
     </row>
     <row r="36">
       <c r="A36" s="11"/>
@@ -5488,6 +5540,7 @@
       <c r="Q36" s="11"/>
       <c r="R36" s="11"/>
       <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
     </row>
     <row r="37">
       <c r="A37" s="11"/>
@@ -5509,6 +5562,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
       <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
     </row>
     <row r="38">
       <c r="A38" s="11"/>
@@ -5530,6 +5584,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
       <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
     </row>
     <row r="39">
       <c r="A39" s="11"/>
@@ -5551,6 +5606,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
       <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
     </row>
     <row r="40">
       <c r="A40" s="11"/>
@@ -5572,6 +5628,7 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
       <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
     </row>
     <row r="41">
       <c r="A41" s="11"/>
@@ -5593,6 +5650,7 @@
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
       <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
     </row>
     <row r="42">
       <c r="A42" s="11"/>
@@ -5614,6 +5672,7 @@
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
       <c r="S42" s="11"/>
+      <c r="T42" s="11"/>
     </row>
     <row r="43">
       <c r="A43" s="11"/>
@@ -5635,6 +5694,7 @@
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
       <c r="S43" s="11"/>
+      <c r="T43" s="11"/>
     </row>
     <row r="44">
       <c r="A44" s="11"/>
@@ -5656,6 +5716,7 @@
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
       <c r="S44" s="11"/>
+      <c r="T44" s="11"/>
     </row>
     <row r="45">
       <c r="A45" s="11"/>
@@ -5677,6 +5738,7 @@
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
       <c r="S45" s="11"/>
+      <c r="T45" s="11"/>
     </row>
     <row r="46">
       <c r="A46" s="11"/>
@@ -5698,6 +5760,7 @@
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
       <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
     </row>
     <row r="47">
       <c r="A47" s="11"/>
@@ -5719,6 +5782,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
       <c r="S47" s="11"/>
+      <c r="T47" s="11"/>
     </row>
     <row r="48">
       <c r="A48" s="11"/>
@@ -5740,6 +5804,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
       <c r="S48" s="11"/>
+      <c r="T48" s="11"/>
     </row>
     <row r="49">
       <c r="A49" s="11"/>
@@ -5761,6 +5826,7 @@
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
       <c r="S49" s="11"/>
+      <c r="T49" s="11"/>
     </row>
     <row r="50">
       <c r="A50" s="11"/>
@@ -5782,6 +5848,7 @@
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
       <c r="S50" s="11"/>
+      <c r="T50" s="11"/>
     </row>
     <row r="51">
       <c r="A51" s="11"/>
@@ -5803,6 +5870,7 @@
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
       <c r="S51" s="11"/>
+      <c r="T51" s="11"/>
     </row>
     <row r="52">
       <c r="A52" s="11"/>
@@ -5824,6 +5892,7 @@
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
       <c r="S52" s="11"/>
+      <c r="T52" s="11"/>
     </row>
     <row r="53">
       <c r="A53" s="11"/>
@@ -5845,6 +5914,7 @@
       <c r="Q53" s="11"/>
       <c r="R53" s="11"/>
       <c r="S53" s="11"/>
+      <c r="T53" s="11"/>
     </row>
     <row r="54">
       <c r="A54" s="11"/>
@@ -5866,6 +5936,7 @@
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
       <c r="S54" s="11"/>
+      <c r="T54" s="11"/>
     </row>
     <row r="55">
       <c r="A55" s="11"/>
@@ -5887,6 +5958,7 @@
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
       <c r="S55" s="11"/>
+      <c r="T55" s="11"/>
     </row>
     <row r="56">
       <c r="A56" s="11"/>
@@ -5908,6 +5980,7 @@
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
       <c r="S56" s="11"/>
+      <c r="T56" s="11"/>
     </row>
     <row r="57">
       <c r="A57" s="11"/>
@@ -5929,6 +6002,7 @@
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
       <c r="S57" s="11"/>
+      <c r="T57" s="11"/>
     </row>
     <row r="58">
       <c r="A58" s="11"/>
@@ -5950,11 +6024,12 @@
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
       <c r="S58" s="11"/>
+      <c r="T58" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F58">
@@ -5970,7 +6045,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
@@ -5995,6 +6070,12 @@
           </x14:formula1>
           <xm:sqref>G5:G58</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>K5:K58</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -6013,122 +6094,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -6154,12 +6235,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3">
@@ -6167,35 +6248,35 @@
         <v>341</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>35</v>
@@ -6206,10 +6287,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>35</v>
@@ -6220,10 +6301,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>35</v>
@@ -6234,16 +6315,16 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -6447,28 +6528,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5">
@@ -6573,42 +6654,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -6616,10 +6697,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -6753,56 +6834,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7">
